--- a/data/求解结果对比-直达声压（RoomMapping）/中型教室1/单声源/【中型教室1】【单声源，三分之一倍频程，A加权，直达声压】【250HZ】- 声压数据_20260422_115551.xlsx
+++ b/data/求解结果对比-直达声压（RoomMapping）/中型教室1/单声源/【中型教室1】【单声源，三分之一倍频程，A加权，直达声压】【250HZ】- 声压数据_20260422_115551.xlsx
@@ -5,7 +5,7 @@
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="E:\AudioSimulationSnap\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="E:\AudioSimulationSnap\data\求解结果对比-直达声压（RoomMapping）\中型教室1\单声源\"/>
     </mc:Choice>
   </mc:AlternateContent>
   <bookViews>
@@ -14,6 +14,9 @@
   <sheets>
     <sheet name="声压数据" sheetId="1" r:id="rId1"/>
   </sheets>
+  <definedNames>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">声压数据!$A$1:$I$1</definedName>
+  </definedNames>
   <calcPr calcId="0"/>
 </workbook>
 </file>
@@ -68,12 +71,18 @@
       <scheme val="minor"/>
     </font>
   </fonts>
-  <fills count="2">
+  <fills count="3">
     <fill>
       <patternFill patternType="none"/>
     </fill>
     <fill>
       <patternFill patternType="gray125"/>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFFF00"/>
+        <bgColor indexed="64"/>
+      </patternFill>
     </fill>
   </fills>
   <borders count="1">
@@ -88,8 +97,9 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="1">
+  <cellXfs count="2">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="0" xfId="0" applyFill="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="常规" xfId="0" builtinId="0"/>
@@ -392,8 +402,13 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:I200"/>
+  <dimension ref="A1:I185"/>
   <sheetFormatPr defaultRowHeight="14" x14ac:dyDescent="0.25"/>
+  <cols>
+    <col min="1" max="3" width="7.54296875" bestFit="1" customWidth="1"/>
+    <col min="4" max="8" width="8.54296875" bestFit="1" customWidth="1"/>
+    <col min="9" max="9" width="13.6328125" bestFit="1" customWidth="1"/>
+  </cols>
   <sheetData>
     <row r="1" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A1" t="s">
@@ -426,205 +441,205 @@
     </row>
     <row r="2" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A2">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="B2">
         <v>1</v>
       </c>
       <c r="C2">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="D2">
-        <v>463</v>
+        <v>513</v>
       </c>
       <c r="E2">
-        <v>251</v>
-      </c>
-      <c r="F2">
-        <v>0.63</v>
-      </c>
-      <c r="G2">
-        <v>8.01</v>
+        <v>213</v>
+      </c>
+      <c r="F2" s="1">
+        <v>0.19</v>
+      </c>
+      <c r="G2" s="1">
+        <v>8.11</v>
       </c>
       <c r="H2">
         <v>1.2</v>
       </c>
       <c r="I2">
-        <v>73.760000000000005</v>
+        <v>72.233999999999995</v>
       </c>
     </row>
     <row r="3" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A3">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="B3">
         <v>1</v>
       </c>
       <c r="C3">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="D3">
-        <v>494</v>
+        <v>537</v>
       </c>
       <c r="E3">
-        <v>251</v>
-      </c>
-      <c r="F3">
-        <v>0.53</v>
-      </c>
-      <c r="G3">
-        <v>7.95</v>
+        <v>213</v>
+      </c>
+      <c r="F3" s="1">
+        <v>0.63</v>
+      </c>
+      <c r="G3" s="1">
+        <v>8.11</v>
       </c>
       <c r="H3">
         <v>1.2</v>
       </c>
       <c r="I3">
-        <v>73.72</v>
+        <v>73.23</v>
       </c>
     </row>
     <row r="4" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A4">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="B4">
         <v>1</v>
       </c>
       <c r="C4">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="D4">
-        <v>525</v>
+        <v>560</v>
       </c>
       <c r="E4">
-        <v>251</v>
-      </c>
-      <c r="F4">
-        <v>1.45</v>
-      </c>
-      <c r="G4">
-        <v>8.02</v>
+        <v>213</v>
+      </c>
+      <c r="F4" s="1">
+        <v>1.05</v>
+      </c>
+      <c r="G4" s="1">
+        <v>8.11</v>
       </c>
       <c r="H4">
         <v>1.2</v>
       </c>
       <c r="I4">
-        <v>75.739999999999995</v>
+        <v>74.16</v>
       </c>
     </row>
     <row r="5" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A5">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="B5">
         <v>1</v>
       </c>
       <c r="C5">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="D5">
-        <v>556</v>
+        <v>584</v>
       </c>
       <c r="E5">
-        <v>251</v>
-      </c>
-      <c r="F5">
-        <v>1.86</v>
-      </c>
-      <c r="G5">
-        <v>8.02</v>
+        <v>213</v>
+      </c>
+      <c r="F5" s="1">
+        <v>1.49</v>
+      </c>
+      <c r="G5" s="1">
+        <v>8.11</v>
       </c>
       <c r="H5">
         <v>1.2</v>
       </c>
       <c r="I5">
-        <v>76.52</v>
+        <v>75.02</v>
       </c>
     </row>
     <row r="6" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A6">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="B6">
         <v>1</v>
       </c>
       <c r="C6">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="D6">
-        <v>587</v>
+        <v>607</v>
       </c>
       <c r="E6">
-        <v>251</v>
-      </c>
-      <c r="F6">
-        <v>2.27</v>
-      </c>
-      <c r="G6">
-        <v>8.02</v>
+        <v>213</v>
+      </c>
+      <c r="F6" s="1">
+        <v>1.91</v>
+      </c>
+      <c r="G6" s="1">
+        <v>8.11</v>
       </c>
       <c r="H6">
         <v>1.2</v>
       </c>
       <c r="I6">
-        <v>775</v>
+        <v>75.989999999999995</v>
       </c>
     </row>
     <row r="7" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A7">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="B7">
         <v>1</v>
       </c>
       <c r="C7">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="D7">
-        <v>618</v>
+        <v>630</v>
       </c>
       <c r="E7">
-        <v>251</v>
-      </c>
-      <c r="F7">
-        <v>2.68</v>
-      </c>
-      <c r="G7">
-        <v>8.02</v>
+        <v>213</v>
+      </c>
+      <c r="F7" s="1">
+        <v>2.34</v>
+      </c>
+      <c r="G7" s="1">
+        <v>8.11</v>
       </c>
       <c r="H7">
         <v>1.2</v>
       </c>
       <c r="I7">
-        <v>7755</v>
+        <v>76.53</v>
       </c>
     </row>
     <row r="8" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A8">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="B8">
         <v>1</v>
       </c>
       <c r="C8">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="D8">
-        <v>649</v>
+        <v>654</v>
       </c>
       <c r="E8">
-        <v>251</v>
-      </c>
-      <c r="F8">
-        <v>3.09</v>
-      </c>
-      <c r="G8">
-        <v>8.02</v>
+        <v>213</v>
+      </c>
+      <c r="F8" s="1">
+        <v>2.78</v>
+      </c>
+      <c r="G8" s="1">
+        <v>8.11</v>
       </c>
       <c r="H8">
         <v>1.2</v>
       </c>
       <c r="I8">
-        <v>77.78</v>
+        <v>76.900000000000006</v>
       </c>
     </row>
     <row r="9" spans="1:9" x14ac:dyDescent="0.25">
@@ -638,22 +653,22 @@
         <v>9</v>
       </c>
       <c r="D9">
-        <v>680</v>
+        <v>701</v>
       </c>
       <c r="E9">
-        <v>251</v>
-      </c>
-      <c r="F9">
-        <v>3.5</v>
-      </c>
-      <c r="G9">
-        <v>8.02</v>
+        <v>213</v>
+      </c>
+      <c r="F9" s="1">
+        <v>3.64</v>
+      </c>
+      <c r="G9" s="1">
+        <v>8.11</v>
       </c>
       <c r="H9">
         <v>1.2</v>
       </c>
       <c r="I9">
-        <v>77.849999999999994</v>
+        <v>77.180000000000007</v>
       </c>
     </row>
     <row r="10" spans="1:9" x14ac:dyDescent="0.25">
@@ -667,22 +682,22 @@
         <v>10</v>
       </c>
       <c r="D10">
-        <v>711</v>
+        <v>724</v>
       </c>
       <c r="E10">
-        <v>251</v>
-      </c>
-      <c r="F10">
-        <v>4.01</v>
-      </c>
-      <c r="G10">
-        <v>8.08</v>
+        <v>213</v>
+      </c>
+      <c r="F10" s="1">
+        <v>4.0599999999999996</v>
+      </c>
+      <c r="G10" s="1">
+        <v>8.11</v>
       </c>
       <c r="H10">
         <v>1.2</v>
       </c>
       <c r="I10">
-        <v>77.78</v>
+        <v>77.134</v>
       </c>
     </row>
     <row r="11" spans="1:9" x14ac:dyDescent="0.25">
@@ -696,22 +711,22 @@
         <v>11</v>
       </c>
       <c r="D11">
-        <v>741</v>
+        <v>748</v>
       </c>
       <c r="E11">
-        <v>251</v>
+        <v>213</v>
       </c>
       <c r="F11">
-        <v>4.32</v>
+        <v>4.5</v>
       </c>
       <c r="G11">
-        <v>8.02</v>
+        <v>8.11</v>
       </c>
       <c r="H11">
         <v>1.2</v>
       </c>
       <c r="I11">
-        <v>77.610799999999998</v>
+        <v>76.84</v>
       </c>
     </row>
     <row r="12" spans="1:9" x14ac:dyDescent="0.25">
@@ -725,22 +740,22 @@
         <v>12</v>
       </c>
       <c r="D12">
-        <v>772</v>
+        <v>771</v>
       </c>
       <c r="E12">
-        <v>251</v>
+        <v>213</v>
       </c>
       <c r="F12">
-        <v>4.83</v>
+        <v>4.92</v>
       </c>
       <c r="G12">
-        <v>8.08</v>
+        <v>8.11</v>
       </c>
       <c r="H12">
         <v>1.2</v>
       </c>
       <c r="I12">
-        <v>77.360799999999998</v>
+        <v>76.63</v>
       </c>
     </row>
     <row r="13" spans="1:9" x14ac:dyDescent="0.25">
@@ -754,22 +769,22 @@
         <v>13</v>
       </c>
       <c r="D13">
-        <v>803</v>
+        <v>795</v>
       </c>
       <c r="E13">
-        <v>251</v>
+        <v>213</v>
       </c>
       <c r="F13">
-        <v>5.24</v>
+        <v>5.36</v>
       </c>
       <c r="G13">
-        <v>8.08</v>
+        <v>8.11</v>
       </c>
       <c r="H13">
         <v>1.2</v>
       </c>
       <c r="I13">
-        <v>77.05</v>
+        <v>76.349999999999994</v>
       </c>
     </row>
     <row r="14" spans="1:9" x14ac:dyDescent="0.25">
@@ -783,22 +798,22 @@
         <v>14</v>
       </c>
       <c r="D14">
-        <v>834</v>
+        <v>818</v>
       </c>
       <c r="E14">
-        <v>251</v>
+        <v>213</v>
       </c>
       <c r="F14">
-        <v>5.65</v>
+        <v>5.78</v>
       </c>
       <c r="G14">
-        <v>8.08</v>
+        <v>8.11</v>
       </c>
       <c r="H14">
         <v>1.2</v>
       </c>
       <c r="I14">
-        <v>76.7</v>
+        <v>76.040000000000006</v>
       </c>
     </row>
     <row r="15" spans="1:9" x14ac:dyDescent="0.25">
@@ -812,22 +827,22 @@
         <v>15</v>
       </c>
       <c r="D15">
-        <v>865</v>
+        <v>842</v>
       </c>
       <c r="E15">
-        <v>251</v>
+        <v>213</v>
       </c>
       <c r="F15">
-        <v>6.05</v>
+        <v>6.22</v>
       </c>
       <c r="G15">
-        <v>8.08</v>
+        <v>8.11</v>
       </c>
       <c r="H15">
         <v>1.2</v>
       </c>
       <c r="I15">
-        <v>76.319999999999993</v>
+        <v>75.7</v>
       </c>
     </row>
     <row r="16" spans="1:9" x14ac:dyDescent="0.25">
@@ -841,22 +856,22 @@
         <v>16</v>
       </c>
       <c r="D16">
-        <v>896</v>
+        <v>865</v>
       </c>
       <c r="E16">
-        <v>251</v>
+        <v>213</v>
       </c>
       <c r="F16">
-        <v>6.42</v>
+        <v>6.65</v>
       </c>
       <c r="G16">
-        <v>8.06</v>
+        <v>8.11</v>
       </c>
       <c r="H16">
         <v>1.2</v>
       </c>
       <c r="I16">
-        <v>75.849999999999994</v>
+        <v>75.38</v>
       </c>
     </row>
     <row r="17" spans="1:9" x14ac:dyDescent="0.25">
@@ -870,390 +885,390 @@
         <v>17</v>
       </c>
       <c r="D17">
-        <v>927</v>
+        <v>888</v>
       </c>
       <c r="E17">
-        <v>251</v>
+        <v>213</v>
       </c>
       <c r="F17">
-        <v>6.82</v>
+        <v>7.07</v>
       </c>
       <c r="G17">
-        <v>8.06</v>
+        <v>8.11</v>
       </c>
       <c r="H17">
         <v>1.2</v>
       </c>
       <c r="I17">
-        <v>75.45</v>
+        <v>74.86</v>
       </c>
     </row>
     <row r="18" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A18">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="B18">
         <v>1</v>
       </c>
       <c r="C18">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="D18">
-        <v>958</v>
+        <v>935</v>
       </c>
       <c r="E18">
-        <v>251</v>
+        <v>213</v>
       </c>
       <c r="F18">
-        <v>7.22</v>
+        <v>7.93</v>
       </c>
       <c r="G18">
-        <v>8.07</v>
+        <v>8.11</v>
       </c>
       <c r="H18">
         <v>1.2</v>
       </c>
       <c r="I18">
-        <v>75.040000000000006</v>
+        <v>74.11</v>
       </c>
     </row>
     <row r="19" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A19">
-        <v>19</v>
+        <v>21</v>
       </c>
       <c r="B19">
+        <v>2</v>
+      </c>
+      <c r="C19">
         <v>1</v>
       </c>
-      <c r="C19">
-        <v>19</v>
-      </c>
       <c r="D19">
-        <v>989</v>
+        <v>513</v>
       </c>
       <c r="E19">
-        <v>251</v>
+        <v>260</v>
       </c>
       <c r="F19">
-        <v>7.63</v>
+        <v>0.19</v>
       </c>
       <c r="G19">
-        <v>8.07</v>
+        <v>7.25</v>
       </c>
       <c r="H19">
         <v>1.2</v>
       </c>
       <c r="I19">
-        <v>74.630799999999994</v>
+        <v>73.02</v>
       </c>
     </row>
     <row r="20" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A20">
-        <v>20</v>
+        <v>22</v>
       </c>
       <c r="B20">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="C20">
-        <v>20</v>
+        <v>2</v>
       </c>
       <c r="D20">
-        <v>1020</v>
+        <v>537</v>
       </c>
       <c r="E20">
-        <v>251</v>
+        <v>260</v>
       </c>
       <c r="F20">
-        <v>8.0399999999999991</v>
+        <v>0.63</v>
       </c>
       <c r="G20">
-        <v>8.06</v>
+        <v>7.25</v>
       </c>
       <c r="H20">
         <v>1.2</v>
       </c>
       <c r="I20">
-        <v>74.220799999999997</v>
+        <v>74.150000000000006</v>
       </c>
     </row>
     <row r="21" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A21">
-        <v>21</v>
+        <v>23</v>
       </c>
       <c r="B21">
         <v>2</v>
       </c>
       <c r="C21">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="D21">
-        <v>432</v>
+        <v>560</v>
       </c>
       <c r="E21">
-        <v>314</v>
+        <v>260</v>
       </c>
       <c r="F21">
-        <v>0.23</v>
+        <v>1.05</v>
       </c>
       <c r="G21">
-        <v>7.18</v>
+        <v>7.25</v>
       </c>
       <c r="H21">
         <v>1.2</v>
       </c>
       <c r="I21">
-        <v>73.319999999999993</v>
+        <v>75.3</v>
       </c>
     </row>
     <row r="22" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A22">
-        <v>22</v>
+        <v>24</v>
       </c>
       <c r="B22">
         <v>2</v>
       </c>
       <c r="C22">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="D22">
-        <v>463</v>
+        <v>584</v>
       </c>
       <c r="E22">
-        <v>314</v>
+        <v>260</v>
       </c>
       <c r="F22">
-        <v>0.64</v>
+        <v>1.49</v>
       </c>
       <c r="G22">
-        <v>7.19</v>
+        <v>7.25</v>
       </c>
       <c r="H22">
         <v>1.2</v>
       </c>
       <c r="I22">
-        <v>747108</v>
+        <v>76.724000000000004</v>
       </c>
     </row>
     <row r="23" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A23">
-        <v>23</v>
+        <v>25</v>
       </c>
       <c r="B23">
         <v>2</v>
       </c>
       <c r="C23">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="D23">
-        <v>494</v>
+        <v>607</v>
       </c>
       <c r="E23">
-        <v>314</v>
+        <v>260</v>
       </c>
       <c r="F23">
-        <v>1.05</v>
+        <v>1.91</v>
       </c>
       <c r="G23">
-        <v>7.19</v>
+        <v>7.25</v>
       </c>
       <c r="H23">
         <v>1.2</v>
       </c>
       <c r="I23">
-        <v>75.98</v>
+        <v>77.58</v>
       </c>
     </row>
     <row r="24" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A24">
-        <v>24</v>
+        <v>26</v>
       </c>
       <c r="B24">
         <v>2</v>
       </c>
       <c r="C24">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="D24">
-        <v>525</v>
+        <v>630</v>
       </c>
       <c r="E24">
-        <v>314</v>
+        <v>260</v>
       </c>
       <c r="F24">
-        <v>1.45</v>
+        <v>2.34</v>
       </c>
       <c r="G24">
-        <v>7.19</v>
+        <v>7.25</v>
       </c>
       <c r="H24">
         <v>1.2</v>
       </c>
       <c r="I24">
-        <v>7718</v>
+        <v>78.22</v>
       </c>
     </row>
     <row r="25" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A25">
-        <v>25</v>
+        <v>27</v>
       </c>
       <c r="B25">
         <v>2</v>
       </c>
       <c r="C25">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="D25">
-        <v>556</v>
+        <v>654</v>
       </c>
       <c r="E25">
-        <v>314</v>
+        <v>260</v>
       </c>
       <c r="F25">
-        <v>1.86</v>
+        <v>2.78</v>
       </c>
       <c r="G25">
-        <v>7.19</v>
+        <v>7.25</v>
       </c>
       <c r="H25">
         <v>1.2</v>
       </c>
       <c r="I25">
-        <v>78.19</v>
+        <v>78.634</v>
       </c>
     </row>
     <row r="26" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A26">
-        <v>26</v>
+        <v>28</v>
       </c>
       <c r="B26">
         <v>2</v>
       </c>
       <c r="C26">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="D26">
-        <v>587</v>
+        <v>677</v>
       </c>
       <c r="E26">
-        <v>314</v>
+        <v>260</v>
       </c>
       <c r="F26">
-        <v>2.27</v>
+        <v>3.2</v>
       </c>
       <c r="G26">
-        <v>7.19</v>
+        <v>7.25</v>
       </c>
       <c r="H26">
         <v>1.2</v>
       </c>
       <c r="I26">
-        <v>78.930000000000007</v>
+        <v>78.81</v>
       </c>
     </row>
     <row r="27" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A27">
-        <v>27</v>
+        <v>29</v>
       </c>
       <c r="B27">
         <v>2</v>
       </c>
       <c r="C27">
-        <v>7</v>
+        <v>9</v>
       </c>
       <c r="D27">
-        <v>618</v>
+        <v>701</v>
       </c>
       <c r="E27">
-        <v>314</v>
+        <v>260</v>
       </c>
       <c r="F27">
-        <v>2.68</v>
+        <v>3.64</v>
       </c>
       <c r="G27">
-        <v>7.19</v>
+        <v>7.25</v>
       </c>
       <c r="H27">
         <v>1.2</v>
       </c>
       <c r="I27">
-        <v>79.400000000000006</v>
+        <v>78.8</v>
       </c>
     </row>
     <row r="28" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A28">
-        <v>28</v>
+        <v>30</v>
       </c>
       <c r="B28">
         <v>2</v>
       </c>
       <c r="C28">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="D28">
-        <v>649</v>
+        <v>724</v>
       </c>
       <c r="E28">
-        <v>314</v>
+        <v>260</v>
       </c>
       <c r="F28">
-        <v>3.09</v>
+        <v>4.0599999999999996</v>
       </c>
       <c r="G28">
-        <v>7.19</v>
+        <v>7.25</v>
       </c>
       <c r="H28">
         <v>1.2</v>
       </c>
       <c r="I28">
-        <v>79.59</v>
+        <v>78.650000000000006</v>
       </c>
     </row>
     <row r="29" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A29">
-        <v>29</v>
+        <v>31</v>
       </c>
       <c r="B29">
         <v>2</v>
       </c>
       <c r="C29">
-        <v>9</v>
+        <v>11</v>
       </c>
       <c r="D29">
-        <v>680</v>
+        <v>748</v>
       </c>
       <c r="E29">
-        <v>314</v>
+        <v>260</v>
       </c>
       <c r="F29">
-        <v>3.5</v>
+        <v>4.5</v>
       </c>
       <c r="G29">
-        <v>7.19</v>
+        <v>7.25</v>
       </c>
       <c r="H29">
         <v>1.2</v>
       </c>
       <c r="I29">
-        <v>79.56</v>
+        <v>78.42</v>
       </c>
     </row>
     <row r="30" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A30">
-        <v>30</v>
+        <v>32</v>
       </c>
       <c r="B30">
         <v>2</v>
       </c>
       <c r="C30">
-        <v>10</v>
+        <v>12</v>
       </c>
       <c r="D30">
-        <v>711</v>
+        <v>771</v>
       </c>
       <c r="E30">
-        <v>314</v>
+        <v>260</v>
       </c>
       <c r="F30">
-        <v>4</v>
+        <v>4.92</v>
       </c>
       <c r="G30">
         <v>7.25</v>
@@ -1262,27 +1277,27 @@
         <v>1.2</v>
       </c>
       <c r="I30">
-        <v>79.48</v>
+        <v>78.06</v>
       </c>
     </row>
     <row r="31" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A31">
-        <v>31</v>
+        <v>33</v>
       </c>
       <c r="B31">
         <v>2</v>
       </c>
       <c r="C31">
-        <v>11</v>
+        <v>13</v>
       </c>
       <c r="D31">
-        <v>741</v>
+        <v>795</v>
       </c>
       <c r="E31">
-        <v>314</v>
+        <v>260</v>
       </c>
       <c r="F31">
-        <v>4.4000000000000004</v>
+        <v>5.36</v>
       </c>
       <c r="G31">
         <v>7.25</v>
@@ -1291,27 +1306,27 @@
         <v>1.2</v>
       </c>
       <c r="I31">
-        <v>79.14</v>
+        <v>77.61</v>
       </c>
     </row>
     <row r="32" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A32">
-        <v>32</v>
+        <v>34</v>
       </c>
       <c r="B32">
         <v>2</v>
       </c>
       <c r="C32">
-        <v>12</v>
+        <v>14</v>
       </c>
       <c r="D32">
-        <v>772</v>
+        <v>818</v>
       </c>
       <c r="E32">
-        <v>314</v>
+        <v>260</v>
       </c>
       <c r="F32">
-        <v>4.8099999999999996</v>
+        <v>5.78</v>
       </c>
       <c r="G32">
         <v>7.25</v>
@@ -1320,27 +1335,27 @@
         <v>1.2</v>
       </c>
       <c r="I32">
-        <v>78.739999999999995</v>
+        <v>77.040000000000006</v>
       </c>
     </row>
     <row r="33" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A33">
-        <v>33</v>
+        <v>35</v>
       </c>
       <c r="B33">
         <v>2</v>
       </c>
       <c r="C33">
-        <v>13</v>
+        <v>15</v>
       </c>
       <c r="D33">
-        <v>803</v>
+        <v>842</v>
       </c>
       <c r="E33">
-        <v>314</v>
+        <v>260</v>
       </c>
       <c r="F33">
-        <v>5.23</v>
+        <v>6.22</v>
       </c>
       <c r="G33">
         <v>7.25</v>
@@ -1349,27 +1364,27 @@
         <v>1.2</v>
       </c>
       <c r="I33">
-        <v>78.25</v>
+        <v>76.599999999999994</v>
       </c>
     </row>
     <row r="34" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A34">
-        <v>34</v>
+        <v>36</v>
       </c>
       <c r="B34">
         <v>2</v>
       </c>
       <c r="C34">
-        <v>14</v>
+        <v>16</v>
       </c>
       <c r="D34">
-        <v>834</v>
+        <v>865</v>
       </c>
       <c r="E34">
-        <v>314</v>
+        <v>260</v>
       </c>
       <c r="F34">
-        <v>5.63</v>
+        <v>6.65</v>
       </c>
       <c r="G34">
         <v>7.25</v>
@@ -1378,27 +1393,27 @@
         <v>1.2</v>
       </c>
       <c r="I34">
-        <v>77.760800000000003</v>
+        <v>76.150000000000006</v>
       </c>
     </row>
     <row r="35" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A35">
-        <v>35</v>
+        <v>37</v>
       </c>
       <c r="B35">
         <v>2</v>
       </c>
       <c r="C35">
-        <v>15</v>
+        <v>17</v>
       </c>
       <c r="D35">
-        <v>865</v>
+        <v>888</v>
       </c>
       <c r="E35">
-        <v>314</v>
+        <v>260</v>
       </c>
       <c r="F35">
-        <v>6.01</v>
+        <v>7.07</v>
       </c>
       <c r="G35">
         <v>7.25</v>
@@ -1407,27 +1422,27 @@
         <v>1.2</v>
       </c>
       <c r="I35">
-        <v>77.209999999999994</v>
+        <v>75.7</v>
       </c>
     </row>
     <row r="36" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A36">
-        <v>36</v>
+        <v>38</v>
       </c>
       <c r="B36">
         <v>2</v>
       </c>
       <c r="C36">
-        <v>16</v>
+        <v>18</v>
       </c>
       <c r="D36">
-        <v>896</v>
+        <v>912</v>
       </c>
       <c r="E36">
-        <v>314</v>
+        <v>260</v>
       </c>
       <c r="F36">
-        <v>6.41</v>
+        <v>7.51</v>
       </c>
       <c r="G36">
         <v>7.25</v>
@@ -1436,723 +1451,723 @@
         <v>1.2</v>
       </c>
       <c r="I36">
-        <v>76.72</v>
+        <v>75.099999999999994</v>
       </c>
     </row>
     <row r="37" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A37">
-        <v>37</v>
+        <v>41</v>
       </c>
       <c r="B37">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="C37">
-        <v>17</v>
+        <v>1</v>
       </c>
       <c r="D37">
-        <v>927</v>
+        <v>513</v>
       </c>
       <c r="E37">
-        <v>314</v>
+        <v>306</v>
       </c>
       <c r="F37">
-        <v>6.81</v>
+        <v>0.19</v>
       </c>
       <c r="G37">
-        <v>7.25</v>
+        <v>6.4</v>
       </c>
       <c r="H37">
         <v>1.2</v>
       </c>
       <c r="I37">
-        <v>76.22</v>
+        <v>73.63</v>
       </c>
     </row>
     <row r="38" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A38">
-        <v>38</v>
+        <v>42</v>
       </c>
       <c r="B38">
+        <v>3</v>
+      </c>
+      <c r="C38">
         <v>2</v>
       </c>
-      <c r="C38">
-        <v>18</v>
-      </c>
       <c r="D38">
-        <v>958</v>
+        <v>537</v>
       </c>
       <c r="E38">
-        <v>314</v>
+        <v>306</v>
       </c>
       <c r="F38">
-        <v>7.21</v>
+        <v>0.63</v>
       </c>
       <c r="G38">
-        <v>7.24</v>
+        <v>6.4</v>
       </c>
       <c r="H38">
         <v>1.2</v>
       </c>
       <c r="I38">
-        <v>75.650000000000006</v>
+        <v>75.260000000000005</v>
       </c>
     </row>
     <row r="39" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A39">
-        <v>39</v>
+        <v>43</v>
       </c>
       <c r="B39">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="C39">
-        <v>19</v>
+        <v>3</v>
       </c>
       <c r="D39">
-        <v>989</v>
+        <v>560</v>
       </c>
       <c r="E39">
-        <v>314</v>
+        <v>306</v>
       </c>
       <c r="F39">
-        <v>7.72</v>
+        <v>1.05</v>
       </c>
       <c r="G39">
-        <v>7.18</v>
+        <v>6.4</v>
       </c>
       <c r="H39">
         <v>1.2</v>
       </c>
       <c r="I39">
-        <v>75.180000000000007</v>
+        <v>76.674000000000007</v>
       </c>
     </row>
     <row r="40" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A40">
-        <v>40</v>
+        <v>44</v>
       </c>
       <c r="B40">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="C40">
-        <v>20</v>
+        <v>4</v>
       </c>
       <c r="D40">
-        <v>1020</v>
+        <v>584</v>
       </c>
       <c r="E40">
-        <v>314</v>
+        <v>306</v>
       </c>
       <c r="F40">
-        <v>8.0399999999999991</v>
+        <v>1.49</v>
       </c>
       <c r="G40">
-        <v>7.23</v>
+        <v>6.4</v>
       </c>
       <c r="H40">
         <v>1.2</v>
       </c>
       <c r="I40">
-        <v>747208</v>
+        <v>78.069999999999993</v>
       </c>
     </row>
     <row r="41" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A41">
-        <v>41</v>
+        <v>46</v>
       </c>
       <c r="B41">
         <v>3</v>
       </c>
       <c r="C41">
-        <v>1</v>
+        <v>6</v>
       </c>
       <c r="D41">
-        <v>432</v>
+        <v>630</v>
       </c>
       <c r="E41">
-        <v>377</v>
+        <v>306</v>
       </c>
       <c r="F41">
-        <v>0.24</v>
+        <v>2.34</v>
       </c>
       <c r="G41">
-        <v>6.36</v>
+        <v>6.4</v>
       </c>
       <c r="H41">
         <v>1.2</v>
       </c>
       <c r="I41">
-        <v>74.290000000000006</v>
+        <v>80.2</v>
       </c>
     </row>
     <row r="42" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A42">
-        <v>42</v>
+        <v>47</v>
       </c>
       <c r="B42">
         <v>3</v>
       </c>
       <c r="C42">
-        <v>2</v>
+        <v>7</v>
       </c>
       <c r="D42">
-        <v>463</v>
+        <v>654</v>
       </c>
       <c r="E42">
-        <v>377</v>
+        <v>306</v>
       </c>
       <c r="F42">
-        <v>0.64</v>
+        <v>2.78</v>
       </c>
       <c r="G42">
-        <v>6.36</v>
+        <v>6.4</v>
       </c>
       <c r="H42">
         <v>1.2</v>
       </c>
       <c r="I42">
-        <v>75.510000000000005</v>
+        <v>80.634</v>
       </c>
     </row>
     <row r="43" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A43">
-        <v>43</v>
+        <v>48</v>
       </c>
       <c r="B43">
         <v>3</v>
       </c>
       <c r="C43">
-        <v>3</v>
+        <v>8</v>
       </c>
       <c r="D43">
-        <v>494</v>
+        <v>677</v>
       </c>
       <c r="E43">
-        <v>377</v>
+        <v>306</v>
       </c>
       <c r="F43">
-        <v>1.05</v>
+        <v>3.2</v>
       </c>
       <c r="G43">
-        <v>6.36</v>
+        <v>6.4</v>
       </c>
       <c r="H43">
         <v>1.2</v>
       </c>
       <c r="I43">
-        <v>77.230800000000002</v>
+        <v>80.739999999999995</v>
       </c>
     </row>
     <row r="44" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A44">
-        <v>44</v>
+        <v>49</v>
       </c>
       <c r="B44">
         <v>3</v>
       </c>
       <c r="C44">
-        <v>4</v>
+        <v>9</v>
       </c>
       <c r="D44">
-        <v>525</v>
+        <v>701</v>
       </c>
       <c r="E44">
-        <v>377</v>
+        <v>306</v>
       </c>
       <c r="F44">
-        <v>1.46</v>
+        <v>3.64</v>
       </c>
       <c r="G44">
-        <v>6.37</v>
+        <v>6.4</v>
       </c>
       <c r="H44">
         <v>1.2</v>
       </c>
       <c r="I44">
-        <v>78.760000000000005</v>
+        <v>80.59</v>
       </c>
     </row>
     <row r="45" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A45">
-        <v>45</v>
+        <v>50</v>
       </c>
       <c r="B45">
         <v>3</v>
       </c>
       <c r="C45">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="D45">
-        <v>556</v>
+        <v>724</v>
       </c>
       <c r="E45">
-        <v>377</v>
+        <v>306</v>
       </c>
       <c r="F45">
-        <v>1.86</v>
+        <v>4.0599999999999996</v>
       </c>
       <c r="G45">
-        <v>6.37</v>
+        <v>6.4</v>
       </c>
       <c r="H45">
         <v>1.2</v>
       </c>
       <c r="I45">
-        <v>80.319999999999993</v>
+        <v>80.28</v>
       </c>
     </row>
     <row r="46" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A46">
-        <v>46</v>
+        <v>51</v>
       </c>
       <c r="B46">
         <v>3</v>
       </c>
       <c r="C46">
-        <v>6</v>
+        <v>11</v>
       </c>
       <c r="D46">
-        <v>587</v>
+        <v>748</v>
       </c>
       <c r="E46">
-        <v>377</v>
+        <v>306</v>
       </c>
       <c r="F46">
-        <v>2.27</v>
+        <v>4.5</v>
       </c>
       <c r="G46">
-        <v>6.37</v>
+        <v>6.4</v>
       </c>
       <c r="H46">
         <v>1.2</v>
       </c>
       <c r="I46">
-        <v>81.25</v>
+        <v>79.8</v>
       </c>
     </row>
     <row r="47" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A47">
-        <v>47</v>
+        <v>52</v>
       </c>
       <c r="B47">
         <v>3</v>
       </c>
       <c r="C47">
-        <v>7</v>
+        <v>12</v>
       </c>
       <c r="D47">
-        <v>618</v>
+        <v>771</v>
       </c>
       <c r="E47">
-        <v>377</v>
+        <v>306</v>
       </c>
       <c r="F47">
-        <v>2.68</v>
+        <v>4.92</v>
       </c>
       <c r="G47">
-        <v>6.37</v>
+        <v>6.4</v>
       </c>
       <c r="H47">
         <v>1.2</v>
       </c>
       <c r="I47">
-        <v>81.72</v>
+        <v>79.260000000000005</v>
       </c>
     </row>
     <row r="48" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A48">
-        <v>48</v>
+        <v>53</v>
       </c>
       <c r="B48">
         <v>3</v>
       </c>
       <c r="C48">
-        <v>8</v>
+        <v>13</v>
       </c>
       <c r="D48">
-        <v>649</v>
+        <v>795</v>
       </c>
       <c r="E48">
-        <v>377</v>
+        <v>306</v>
       </c>
       <c r="F48">
-        <v>3.08</v>
+        <v>5.36</v>
       </c>
       <c r="G48">
-        <v>6.37</v>
+        <v>6.4</v>
       </c>
       <c r="H48">
         <v>1.2</v>
       </c>
       <c r="I48">
-        <v>81.78</v>
+        <v>78.510000000000005</v>
       </c>
     </row>
     <row r="49" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A49">
-        <v>49</v>
+        <v>54</v>
       </c>
       <c r="B49">
         <v>3</v>
       </c>
       <c r="C49">
-        <v>9</v>
+        <v>14</v>
       </c>
       <c r="D49">
-        <v>680</v>
+        <v>818</v>
       </c>
       <c r="E49">
-        <v>377</v>
+        <v>306</v>
       </c>
       <c r="F49">
-        <v>3.49</v>
+        <v>5.78</v>
       </c>
       <c r="G49">
-        <v>6.37</v>
+        <v>6.4</v>
       </c>
       <c r="H49">
         <v>1.2</v>
       </c>
       <c r="I49">
-        <v>81.55</v>
+        <v>77.959999999999994</v>
       </c>
     </row>
     <row r="50" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A50">
-        <v>50</v>
+        <v>56</v>
       </c>
       <c r="B50">
         <v>3</v>
       </c>
       <c r="C50">
-        <v>10</v>
+        <v>16</v>
       </c>
       <c r="D50">
-        <v>711</v>
+        <v>865</v>
       </c>
       <c r="E50">
-        <v>377</v>
+        <v>306</v>
       </c>
       <c r="F50">
-        <v>3.89</v>
+        <v>6.65</v>
       </c>
       <c r="G50">
-        <v>6.37</v>
+        <v>6.4</v>
       </c>
       <c r="H50">
         <v>1.2</v>
       </c>
       <c r="I50">
-        <v>81.13</v>
+        <v>76.819999999999993</v>
       </c>
     </row>
     <row r="51" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A51">
-        <v>51</v>
+        <v>57</v>
       </c>
       <c r="B51">
         <v>3</v>
       </c>
       <c r="C51">
-        <v>11</v>
+        <v>17</v>
       </c>
       <c r="D51">
-        <v>741</v>
+        <v>888</v>
       </c>
       <c r="E51">
-        <v>377</v>
+        <v>306</v>
       </c>
       <c r="F51">
-        <v>4.3</v>
+        <v>7.07</v>
       </c>
       <c r="G51">
-        <v>6.37</v>
+        <v>6.4</v>
       </c>
       <c r="H51">
         <v>1.2</v>
       </c>
       <c r="I51">
-        <v>80.569999999999993</v>
+        <v>76.209999999999994</v>
       </c>
     </row>
     <row r="52" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A52">
-        <v>52</v>
+        <v>58</v>
       </c>
       <c r="B52">
         <v>3</v>
       </c>
       <c r="C52">
-        <v>12</v>
+        <v>18</v>
       </c>
       <c r="D52">
-        <v>772</v>
+        <v>912</v>
       </c>
       <c r="E52">
-        <v>377</v>
+        <v>306</v>
       </c>
       <c r="F52">
-        <v>4.8099999999999996</v>
+        <v>7.51</v>
       </c>
       <c r="G52">
-        <v>6.43</v>
+        <v>6.4</v>
       </c>
       <c r="H52">
         <v>1.2</v>
       </c>
       <c r="I52">
-        <v>79.959999999999994</v>
+        <v>75.7</v>
       </c>
     </row>
     <row r="53" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A53">
-        <v>53</v>
+        <v>59</v>
       </c>
       <c r="B53">
         <v>3</v>
       </c>
       <c r="C53">
-        <v>13</v>
+        <v>19</v>
       </c>
       <c r="D53">
-        <v>803</v>
+        <v>935</v>
       </c>
       <c r="E53">
-        <v>377</v>
+        <v>306</v>
       </c>
       <c r="F53">
-        <v>5.2</v>
+        <v>7.93</v>
       </c>
       <c r="G53">
-        <v>6.42</v>
+        <v>6.4</v>
       </c>
       <c r="H53">
         <v>1.2</v>
       </c>
       <c r="I53">
-        <v>79.36</v>
+        <v>75.2</v>
       </c>
     </row>
     <row r="54" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A54">
-        <v>54</v>
+        <v>61</v>
       </c>
       <c r="B54">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="C54">
-        <v>14</v>
+        <v>1</v>
       </c>
       <c r="D54">
-        <v>834</v>
+        <v>513</v>
       </c>
       <c r="E54">
-        <v>377</v>
+        <v>353</v>
       </c>
       <c r="F54">
-        <v>5.61</v>
+        <v>0.19</v>
       </c>
       <c r="G54">
-        <v>6.43</v>
+        <v>5.54</v>
       </c>
       <c r="H54">
         <v>1.2</v>
       </c>
       <c r="I54">
-        <v>78.69</v>
+        <v>75.099999999999994</v>
       </c>
     </row>
     <row r="55" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A55">
-        <v>55</v>
+        <v>62</v>
       </c>
       <c r="B55">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="C55">
-        <v>15</v>
+        <v>2</v>
       </c>
       <c r="D55">
-        <v>865</v>
+        <v>537</v>
       </c>
       <c r="E55">
-        <v>377</v>
+        <v>353</v>
       </c>
       <c r="F55">
-        <v>5.99</v>
+        <v>0.63</v>
       </c>
       <c r="G55">
-        <v>6.42</v>
+        <v>5.54</v>
       </c>
       <c r="H55">
         <v>1.2</v>
       </c>
       <c r="I55">
-        <v>78.010800000000003</v>
+        <v>76.41</v>
       </c>
     </row>
     <row r="56" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A56">
-        <v>56</v>
+        <v>63</v>
       </c>
       <c r="B56">
+        <v>4</v>
+      </c>
+      <c r="C56">
         <v>3</v>
       </c>
-      <c r="C56">
-        <v>16</v>
-      </c>
       <c r="D56">
-        <v>896</v>
+        <v>560</v>
       </c>
       <c r="E56">
-        <v>377</v>
+        <v>353</v>
       </c>
       <c r="F56">
-        <v>6.41</v>
+        <v>1.05</v>
       </c>
       <c r="G56">
-        <v>6.44</v>
+        <v>5.54</v>
       </c>
       <c r="H56">
         <v>1.2</v>
       </c>
       <c r="I56">
-        <v>77.349999999999994</v>
+        <v>73.510000000000005</v>
       </c>
     </row>
     <row r="57" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A57">
-        <v>57</v>
+        <v>64</v>
       </c>
       <c r="B57">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="C57">
-        <v>17</v>
+        <v>4</v>
       </c>
       <c r="D57">
-        <v>927</v>
+        <v>584</v>
       </c>
       <c r="E57">
-        <v>377</v>
+        <v>353</v>
       </c>
       <c r="F57">
-        <v>6.9</v>
+        <v>1.49</v>
       </c>
       <c r="G57">
-        <v>6.39</v>
+        <v>5.54</v>
       </c>
       <c r="H57">
         <v>1.2</v>
       </c>
       <c r="I57">
-        <v>76.77</v>
+        <v>79</v>
       </c>
     </row>
     <row r="58" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A58">
-        <v>58</v>
+        <v>65</v>
       </c>
       <c r="B58">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="C58">
-        <v>18</v>
+        <v>5</v>
       </c>
       <c r="D58">
-        <v>958</v>
+        <v>607</v>
       </c>
       <c r="E58">
-        <v>377</v>
+        <v>353</v>
       </c>
       <c r="F58">
-        <v>7.29</v>
+        <v>1.91</v>
       </c>
       <c r="G58">
-        <v>6.39</v>
+        <v>5.54</v>
       </c>
       <c r="H58">
         <v>1.2</v>
       </c>
       <c r="I58">
-        <v>76.23</v>
+        <v>81.31</v>
       </c>
     </row>
     <row r="59" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A59">
-        <v>59</v>
+        <v>66</v>
       </c>
       <c r="B59">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="C59">
-        <v>19</v>
+        <v>6</v>
       </c>
       <c r="D59">
-        <v>989</v>
+        <v>630</v>
       </c>
       <c r="E59">
-        <v>377</v>
+        <v>353</v>
       </c>
       <c r="F59">
-        <v>7.7</v>
+        <v>2.34</v>
       </c>
       <c r="G59">
-        <v>6.39</v>
+        <v>5.54</v>
       </c>
       <c r="H59">
         <v>1.2</v>
       </c>
       <c r="I59">
-        <v>75.680000000000007</v>
+        <v>82.45</v>
       </c>
     </row>
     <row r="60" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A60">
-        <v>60</v>
+        <v>67</v>
       </c>
       <c r="B60">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="C60">
-        <v>20</v>
+        <v>7</v>
       </c>
       <c r="D60">
-        <v>1020</v>
+        <v>654</v>
       </c>
       <c r="E60">
-        <v>377</v>
+        <v>353</v>
       </c>
       <c r="F60">
-        <v>8.08</v>
+        <v>2.78</v>
       </c>
       <c r="G60">
-        <v>6.36</v>
+        <v>5.54</v>
       </c>
       <c r="H60">
         <v>1.2</v>
       </c>
       <c r="I60">
-        <v>75.069999999999993</v>
+        <v>83.22</v>
       </c>
     </row>
     <row r="61" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A61">
-        <v>61</v>
+        <v>68</v>
       </c>
       <c r="B61">
         <v>4</v>
       </c>
       <c r="C61">
-        <v>1</v>
+        <v>8</v>
       </c>
       <c r="D61">
-        <v>432</v>
+        <v>677</v>
       </c>
       <c r="E61">
-        <v>440</v>
+        <v>353</v>
       </c>
       <c r="F61">
-        <v>0.18</v>
+        <v>3.2</v>
       </c>
       <c r="G61">
         <v>5.54</v>
@@ -2161,56 +2176,56 @@
         <v>1.2</v>
       </c>
       <c r="I61">
-        <v>75.91</v>
+        <v>83.134</v>
       </c>
     </row>
     <row r="62" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A62">
-        <v>62</v>
+        <v>69</v>
       </c>
       <c r="B62">
         <v>4</v>
       </c>
       <c r="C62">
-        <v>2</v>
+        <v>9</v>
       </c>
       <c r="D62">
-        <v>463</v>
+        <v>701</v>
       </c>
       <c r="E62">
-        <v>440</v>
+        <v>353</v>
       </c>
       <c r="F62">
-        <v>0.66</v>
+        <v>3.64</v>
       </c>
       <c r="G62">
-        <v>5.55</v>
+        <v>5.54</v>
       </c>
       <c r="H62">
         <v>1.2</v>
       </c>
       <c r="I62">
-        <v>77</v>
+        <v>82.43</v>
       </c>
     </row>
     <row r="63" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A63">
-        <v>63</v>
+        <v>70</v>
       </c>
       <c r="B63">
         <v>4</v>
       </c>
       <c r="C63">
-        <v>3</v>
+        <v>10</v>
       </c>
       <c r="D63">
-        <v>494</v>
+        <v>724</v>
       </c>
       <c r="E63">
-        <v>440</v>
+        <v>353</v>
       </c>
       <c r="F63">
-        <v>1.05</v>
+        <v>4.0599999999999996</v>
       </c>
       <c r="G63">
         <v>5.54</v>
@@ -2219,752 +2234,752 @@
         <v>1.2</v>
       </c>
       <c r="I63">
-        <v>78.45</v>
+        <v>81.790000000000006</v>
       </c>
     </row>
     <row r="64" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A64">
-        <v>64</v>
+        <v>71</v>
       </c>
       <c r="B64">
         <v>4</v>
       </c>
       <c r="C64">
-        <v>4</v>
+        <v>11</v>
       </c>
       <c r="D64">
-        <v>525</v>
+        <v>748</v>
       </c>
       <c r="E64">
-        <v>440</v>
+        <v>353</v>
       </c>
       <c r="F64">
-        <v>1.47</v>
+        <v>4.5</v>
       </c>
       <c r="G64">
-        <v>5.55</v>
+        <v>5.54</v>
       </c>
       <c r="H64">
         <v>1.2</v>
       </c>
       <c r="I64">
-        <v>80.33</v>
+        <v>81.08</v>
       </c>
     </row>
     <row r="65" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A65">
-        <v>65</v>
+        <v>72</v>
       </c>
       <c r="B65">
         <v>4</v>
       </c>
       <c r="C65">
-        <v>5</v>
+        <v>12</v>
       </c>
       <c r="D65">
-        <v>556</v>
+        <v>771</v>
       </c>
       <c r="E65">
-        <v>440</v>
+        <v>353</v>
       </c>
       <c r="F65">
-        <v>1.87</v>
+        <v>4.92</v>
       </c>
       <c r="G65">
-        <v>5.55</v>
+        <v>5.54</v>
       </c>
       <c r="H65">
         <v>1.2</v>
       </c>
       <c r="I65">
-        <v>82.46</v>
+        <v>80.34</v>
       </c>
     </row>
     <row r="66" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A66">
-        <v>66</v>
+        <v>73</v>
       </c>
       <c r="B66">
         <v>4</v>
       </c>
       <c r="C66">
-        <v>6</v>
+        <v>13</v>
       </c>
       <c r="D66">
-        <v>587</v>
+        <v>795</v>
       </c>
       <c r="E66">
-        <v>440</v>
+        <v>353</v>
       </c>
       <c r="F66">
-        <v>2.2799999999999998</v>
+        <v>5.36</v>
       </c>
       <c r="G66">
-        <v>5.55</v>
+        <v>5.54</v>
       </c>
       <c r="H66">
         <v>1.2</v>
       </c>
       <c r="I66">
-        <v>83.7</v>
+        <v>79.48</v>
       </c>
     </row>
     <row r="67" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A67">
-        <v>67</v>
+        <v>74</v>
       </c>
       <c r="B67">
         <v>4</v>
       </c>
       <c r="C67">
-        <v>7</v>
+        <v>14</v>
       </c>
       <c r="D67">
-        <v>618</v>
+        <v>818</v>
       </c>
       <c r="E67">
-        <v>440</v>
+        <v>353</v>
       </c>
       <c r="F67">
-        <v>2.68</v>
+        <v>5.78</v>
       </c>
       <c r="G67">
-        <v>5.55</v>
+        <v>5.54</v>
       </c>
       <c r="H67">
         <v>1.2</v>
       </c>
       <c r="I67">
-        <v>84.05</v>
+        <v>78.760000000000005</v>
       </c>
     </row>
     <row r="68" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A68">
-        <v>68</v>
+        <v>75</v>
       </c>
       <c r="B68">
         <v>4</v>
       </c>
       <c r="C68">
-        <v>8</v>
+        <v>15</v>
       </c>
       <c r="D68">
-        <v>649</v>
+        <v>842</v>
       </c>
       <c r="E68">
-        <v>440</v>
+        <v>353</v>
       </c>
       <c r="F68">
-        <v>3.09</v>
+        <v>6.22</v>
       </c>
       <c r="G68">
-        <v>5.55</v>
+        <v>5.54</v>
       </c>
       <c r="H68">
         <v>1.2</v>
       </c>
       <c r="I68">
-        <v>83.89</v>
+        <v>78.08</v>
       </c>
     </row>
     <row r="69" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A69">
-        <v>69</v>
+        <v>76</v>
       </c>
       <c r="B69">
         <v>4</v>
       </c>
       <c r="C69">
-        <v>9</v>
+        <v>16</v>
       </c>
       <c r="D69">
-        <v>680</v>
+        <v>865</v>
       </c>
       <c r="E69">
-        <v>440</v>
+        <v>353</v>
       </c>
       <c r="F69">
-        <v>3.49</v>
+        <v>6.65</v>
       </c>
       <c r="G69">
-        <v>5.55</v>
+        <v>5.54</v>
       </c>
       <c r="H69">
         <v>1.2</v>
       </c>
       <c r="I69">
-        <v>83.36</v>
+        <v>77.28</v>
       </c>
     </row>
     <row r="70" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A70">
-        <v>70</v>
+        <v>77</v>
       </c>
       <c r="B70">
         <v>4</v>
       </c>
       <c r="C70">
-        <v>10</v>
+        <v>17</v>
       </c>
       <c r="D70">
-        <v>711</v>
+        <v>888</v>
       </c>
       <c r="E70">
-        <v>440</v>
+        <v>353</v>
       </c>
       <c r="F70">
-        <v>3.99</v>
+        <v>7.07</v>
       </c>
       <c r="G70">
-        <v>5.49</v>
+        <v>5.54</v>
       </c>
       <c r="H70">
         <v>1.2</v>
       </c>
       <c r="I70">
-        <v>82.62</v>
+        <v>76.7</v>
       </c>
     </row>
     <row r="71" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A71">
-        <v>71</v>
+        <v>78</v>
       </c>
       <c r="B71">
         <v>4</v>
       </c>
       <c r="C71">
-        <v>11</v>
+        <v>18</v>
       </c>
       <c r="D71">
-        <v>741</v>
+        <v>912</v>
       </c>
       <c r="E71">
-        <v>440</v>
+        <v>353</v>
       </c>
       <c r="F71">
-        <v>4.4000000000000004</v>
+        <v>7.51</v>
       </c>
       <c r="G71">
-        <v>5.5</v>
+        <v>5.54</v>
       </c>
       <c r="H71">
         <v>1.2</v>
       </c>
       <c r="I71">
-        <v>81.81</v>
+        <v>76.099999999999994</v>
       </c>
     </row>
     <row r="72" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A72">
-        <v>72</v>
+        <v>79</v>
       </c>
       <c r="B72">
         <v>4</v>
       </c>
       <c r="C72">
-        <v>12</v>
+        <v>19</v>
       </c>
       <c r="D72">
-        <v>772</v>
+        <v>935</v>
       </c>
       <c r="E72">
-        <v>440</v>
+        <v>353</v>
       </c>
       <c r="F72">
-        <v>4.8</v>
+        <v>7.93</v>
       </c>
       <c r="G72">
-        <v>5.5</v>
+        <v>5.54</v>
       </c>
       <c r="H72">
         <v>1.2</v>
       </c>
       <c r="I72">
-        <v>80.97</v>
+        <v>75.42</v>
       </c>
     </row>
     <row r="73" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A73">
-        <v>73</v>
+        <v>80</v>
       </c>
       <c r="B73">
         <v>4</v>
       </c>
       <c r="C73">
-        <v>13</v>
+        <v>20</v>
       </c>
       <c r="D73">
-        <v>803</v>
+        <v>959</v>
       </c>
       <c r="E73">
-        <v>440</v>
+        <v>353</v>
       </c>
       <c r="F73">
-        <v>5.19</v>
+        <v>8.3699999999999992</v>
       </c>
       <c r="G73">
-        <v>5.49</v>
+        <v>5.54</v>
       </c>
       <c r="H73">
         <v>1.2</v>
       </c>
       <c r="I73">
-        <v>80.16</v>
+        <v>74.900000000000006</v>
       </c>
     </row>
     <row r="74" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A74">
-        <v>74</v>
+        <v>81</v>
       </c>
       <c r="B74">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="C74">
-        <v>14</v>
+        <v>1</v>
       </c>
       <c r="D74">
-        <v>834</v>
+        <v>513</v>
       </c>
       <c r="E74">
-        <v>440</v>
+        <v>400</v>
       </c>
       <c r="F74">
-        <v>5.59</v>
+        <v>0.19</v>
       </c>
       <c r="G74">
-        <v>5.5</v>
+        <v>4.68</v>
       </c>
       <c r="H74">
         <v>1.2</v>
       </c>
       <c r="I74">
-        <v>79.25</v>
+        <v>76.650000000000006</v>
       </c>
     </row>
     <row r="75" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A75">
-        <v>75</v>
+        <v>83</v>
       </c>
       <c r="B75">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="C75">
-        <v>15</v>
+        <v>3</v>
       </c>
       <c r="D75">
-        <v>865</v>
+        <v>560</v>
       </c>
       <c r="E75">
-        <v>440</v>
+        <v>400</v>
       </c>
       <c r="F75">
-        <v>5.98</v>
+        <v>1.05</v>
       </c>
       <c r="G75">
-        <v>5.5</v>
+        <v>4.68</v>
       </c>
       <c r="H75">
         <v>1.2</v>
       </c>
       <c r="I75">
-        <v>78.52</v>
+        <v>79.290000000000006</v>
       </c>
     </row>
     <row r="76" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A76">
-        <v>76</v>
+        <v>84</v>
       </c>
       <c r="B76">
+        <v>5</v>
+      </c>
+      <c r="C76">
         <v>4</v>
       </c>
-      <c r="C76">
-        <v>16</v>
-      </c>
       <c r="D76">
-        <v>896</v>
+        <v>584</v>
       </c>
       <c r="E76">
-        <v>440</v>
+        <v>400</v>
       </c>
       <c r="F76">
-        <v>6.48</v>
+        <v>1.49</v>
       </c>
       <c r="G76">
-        <v>5.55</v>
+        <v>4.68</v>
       </c>
       <c r="H76">
         <v>1.2</v>
       </c>
       <c r="I76">
-        <v>77.84</v>
+        <v>81.209999999999994</v>
       </c>
     </row>
     <row r="77" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A77">
-        <v>77</v>
+        <v>85</v>
       </c>
       <c r="B77">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="C77">
-        <v>17</v>
+        <v>5</v>
       </c>
       <c r="D77">
-        <v>927</v>
+        <v>607</v>
       </c>
       <c r="E77">
-        <v>440</v>
+        <v>400</v>
       </c>
       <c r="F77">
-        <v>6.85</v>
+        <v>1.91</v>
       </c>
       <c r="G77">
-        <v>5.54</v>
+        <v>4.68</v>
       </c>
       <c r="H77">
         <v>1.2</v>
       </c>
       <c r="I77">
-        <v>77</v>
+        <v>83.23</v>
       </c>
     </row>
     <row r="78" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A78">
-        <v>78</v>
+        <v>86</v>
       </c>
       <c r="B78">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="C78">
-        <v>18</v>
+        <v>6</v>
       </c>
       <c r="D78">
-        <v>958</v>
+        <v>630</v>
       </c>
       <c r="E78">
-        <v>440</v>
+        <v>400</v>
       </c>
       <c r="F78">
-        <v>7.27</v>
+        <v>2.34</v>
       </c>
       <c r="G78">
-        <v>5.5</v>
+        <v>4.68</v>
       </c>
       <c r="H78">
         <v>1.2</v>
       </c>
       <c r="I78">
-        <v>76.510000000000005</v>
+        <v>85.01</v>
       </c>
     </row>
     <row r="79" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A79">
-        <v>79</v>
+        <v>87</v>
       </c>
       <c r="B79">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="C79">
-        <v>19</v>
+        <v>7</v>
       </c>
       <c r="D79">
-        <v>989</v>
+        <v>654</v>
       </c>
       <c r="E79">
-        <v>440</v>
+        <v>400</v>
       </c>
       <c r="F79">
-        <v>7.66</v>
+        <v>2.78</v>
       </c>
       <c r="G79">
-        <v>5.51</v>
+        <v>4.68</v>
       </c>
       <c r="H79">
         <v>1.2</v>
       </c>
       <c r="I79">
-        <v>75.849999999999994</v>
+        <v>85.31</v>
       </c>
     </row>
     <row r="80" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A80">
-        <v>80</v>
+        <v>88</v>
       </c>
       <c r="B80">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="C80">
-        <v>20</v>
+        <v>8</v>
       </c>
       <c r="D80">
-        <v>1020</v>
+        <v>677</v>
       </c>
       <c r="E80">
-        <v>440</v>
+        <v>400</v>
       </c>
       <c r="F80">
-        <v>8.0500000000000007</v>
+        <v>3.2</v>
       </c>
       <c r="G80">
-        <v>5.51</v>
+        <v>4.68</v>
       </c>
       <c r="H80">
         <v>1.2</v>
       </c>
       <c r="I80">
-        <v>75.319999999999993</v>
+        <v>84.91</v>
       </c>
     </row>
     <row r="81" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A81">
-        <v>81</v>
+        <v>89</v>
       </c>
       <c r="B81">
         <v>5</v>
       </c>
       <c r="C81">
-        <v>1</v>
+        <v>9</v>
       </c>
       <c r="D81">
-        <v>432</v>
+        <v>701</v>
       </c>
       <c r="E81">
-        <v>503</v>
+        <v>400</v>
       </c>
       <c r="F81">
-        <v>0.26</v>
+        <v>3.64</v>
       </c>
       <c r="G81">
-        <v>4.74</v>
+        <v>4.68</v>
       </c>
       <c r="H81">
         <v>1.2</v>
       </c>
       <c r="I81">
-        <v>77310</v>
+        <v>84.12</v>
       </c>
     </row>
     <row r="82" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A82">
-        <v>82</v>
+        <v>90</v>
       </c>
       <c r="B82">
         <v>5</v>
       </c>
       <c r="C82">
-        <v>2</v>
+        <v>10</v>
       </c>
       <c r="D82">
-        <v>463</v>
+        <v>724</v>
       </c>
       <c r="E82">
-        <v>503</v>
+        <v>400</v>
       </c>
       <c r="F82">
-        <v>0.66</v>
+        <v>4.0599999999999996</v>
       </c>
       <c r="G82">
-        <v>4.7300000000000004</v>
+        <v>4.68</v>
       </c>
       <c r="H82">
         <v>1.2</v>
       </c>
       <c r="I82">
-        <v>78.36</v>
+        <v>83.18</v>
       </c>
     </row>
     <row r="83" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A83">
-        <v>83</v>
+        <v>91</v>
       </c>
       <c r="B83">
         <v>5</v>
       </c>
       <c r="C83">
-        <v>3</v>
+        <v>11</v>
       </c>
       <c r="D83">
-        <v>494</v>
+        <v>748</v>
       </c>
       <c r="E83">
-        <v>503</v>
+        <v>400</v>
       </c>
       <c r="F83">
-        <v>1.07</v>
+        <v>4.5</v>
       </c>
       <c r="G83">
-        <v>4.7300000000000004</v>
+        <v>4.68</v>
       </c>
       <c r="H83">
         <v>1.2</v>
       </c>
       <c r="I83">
-        <v>79.7</v>
+        <v>81.99</v>
       </c>
     </row>
     <row r="84" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A84">
-        <v>84</v>
+        <v>92</v>
       </c>
       <c r="B84">
         <v>5</v>
       </c>
       <c r="C84">
-        <v>4</v>
+        <v>12</v>
       </c>
       <c r="D84">
-        <v>525</v>
+        <v>771</v>
       </c>
       <c r="E84">
-        <v>503</v>
+        <v>400</v>
       </c>
       <c r="F84">
-        <v>1.47</v>
+        <v>4.92</v>
       </c>
       <c r="G84">
-        <v>4.7300000000000004</v>
+        <v>4.68</v>
       </c>
       <c r="H84">
         <v>1.2</v>
       </c>
       <c r="I84">
-        <v>81.52</v>
+        <v>81.06</v>
       </c>
     </row>
     <row r="85" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A85">
-        <v>85</v>
+        <v>93</v>
       </c>
       <c r="B85">
         <v>5</v>
       </c>
       <c r="C85">
-        <v>5</v>
+        <v>13</v>
       </c>
       <c r="D85">
-        <v>556</v>
+        <v>795</v>
       </c>
       <c r="E85">
-        <v>503</v>
+        <v>400</v>
       </c>
       <c r="F85">
-        <v>1.88</v>
+        <v>5.36</v>
       </c>
       <c r="G85">
-        <v>4.74</v>
+        <v>4.68</v>
       </c>
       <c r="H85">
         <v>1.2</v>
       </c>
       <c r="I85">
-        <v>83.96</v>
+        <v>79.95</v>
       </c>
     </row>
     <row r="86" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A86">
-        <v>86</v>
+        <v>94</v>
       </c>
       <c r="B86">
         <v>5</v>
       </c>
       <c r="C86">
-        <v>6</v>
+        <v>14</v>
       </c>
       <c r="D86">
-        <v>587</v>
+        <v>818</v>
       </c>
       <c r="E86">
-        <v>503</v>
+        <v>400</v>
       </c>
       <c r="F86">
-        <v>2.2799999999999998</v>
+        <v>5.78</v>
       </c>
       <c r="G86">
-        <v>4.7300000000000004</v>
+        <v>4.68</v>
       </c>
       <c r="H86">
         <v>1.2</v>
       </c>
       <c r="I86">
-        <v>85.42</v>
+        <v>79.14</v>
       </c>
     </row>
     <row r="87" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A87">
-        <v>87</v>
+        <v>95</v>
       </c>
       <c r="B87">
         <v>5</v>
       </c>
       <c r="C87">
-        <v>7</v>
+        <v>15</v>
       </c>
       <c r="D87">
-        <v>618</v>
+        <v>842</v>
       </c>
       <c r="E87">
-        <v>503</v>
+        <v>400</v>
       </c>
       <c r="F87">
-        <v>2.68</v>
+        <v>6.22</v>
       </c>
       <c r="G87">
-        <v>4.7300000000000004</v>
+        <v>4.68</v>
       </c>
       <c r="H87">
         <v>1.2</v>
       </c>
       <c r="I87">
-        <v>85.84</v>
+        <v>78.37</v>
       </c>
     </row>
     <row r="88" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A88">
-        <v>88</v>
+        <v>96</v>
       </c>
       <c r="B88">
         <v>5</v>
       </c>
       <c r="C88">
-        <v>8</v>
+        <v>16</v>
       </c>
       <c r="D88">
-        <v>649</v>
+        <v>865</v>
       </c>
       <c r="E88">
-        <v>503</v>
+        <v>400</v>
       </c>
       <c r="F88">
-        <v>3.09</v>
+        <v>6.65</v>
       </c>
       <c r="G88">
-        <v>4.7300000000000004</v>
+        <v>4.68</v>
       </c>
       <c r="H88">
         <v>1.2</v>
       </c>
       <c r="I88">
-        <v>85.42</v>
+        <v>77.5</v>
       </c>
     </row>
     <row r="89" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A89">
-        <v>89</v>
+        <v>97</v>
       </c>
       <c r="B89">
         <v>5</v>
       </c>
       <c r="C89">
-        <v>9</v>
+        <v>17</v>
       </c>
       <c r="D89">
-        <v>680</v>
+        <v>888</v>
       </c>
       <c r="E89">
-        <v>503</v>
+        <v>400</v>
       </c>
       <c r="F89">
-        <v>3.59</v>
+        <v>7.07</v>
       </c>
       <c r="G89">
         <v>4.68</v>
@@ -2973,27 +2988,27 @@
         <v>1.2</v>
       </c>
       <c r="I89">
-        <v>84.57</v>
+        <v>76.84</v>
       </c>
     </row>
     <row r="90" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A90">
-        <v>90</v>
+        <v>98</v>
       </c>
       <c r="B90">
         <v>5</v>
       </c>
       <c r="C90">
-        <v>10</v>
+        <v>18</v>
       </c>
       <c r="D90">
-        <v>711</v>
+        <v>912</v>
       </c>
       <c r="E90">
-        <v>503</v>
+        <v>400</v>
       </c>
       <c r="F90">
-        <v>4</v>
+        <v>7.51</v>
       </c>
       <c r="G90">
         <v>4.68</v>
@@ -3002,897 +3017,897 @@
         <v>1.2</v>
       </c>
       <c r="I90">
-        <v>83.55</v>
+        <v>76.23</v>
       </c>
     </row>
     <row r="91" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A91">
-        <v>91</v>
+        <v>99</v>
       </c>
       <c r="B91">
         <v>5</v>
       </c>
       <c r="C91">
-        <v>11</v>
+        <v>19</v>
       </c>
       <c r="D91">
-        <v>741</v>
+        <v>935</v>
       </c>
       <c r="E91">
-        <v>503</v>
+        <v>400</v>
       </c>
       <c r="F91">
-        <v>4.4000000000000004</v>
+        <v>7.93</v>
       </c>
       <c r="G91">
-        <v>4.6900000000000004</v>
+        <v>4.68</v>
       </c>
       <c r="H91">
         <v>1.2</v>
       </c>
       <c r="I91">
-        <v>82.5</v>
+        <v>75.53</v>
       </c>
     </row>
     <row r="92" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A92">
-        <v>92</v>
+        <v>100</v>
       </c>
       <c r="B92">
         <v>5</v>
       </c>
       <c r="C92">
-        <v>12</v>
+        <v>20</v>
       </c>
       <c r="D92">
-        <v>772</v>
+        <v>959</v>
       </c>
       <c r="E92">
-        <v>503</v>
+        <v>400</v>
       </c>
       <c r="F92">
-        <v>4.8</v>
+        <v>8.3699999999999992</v>
       </c>
       <c r="G92">
-        <v>4.6900000000000004</v>
+        <v>4.68</v>
       </c>
       <c r="H92">
         <v>1.2</v>
       </c>
       <c r="I92">
-        <v>81.5</v>
+        <v>74.989999999999995</v>
       </c>
     </row>
     <row r="93" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A93">
-        <v>93</v>
+        <v>102</v>
       </c>
       <c r="B93">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="C93">
-        <v>13</v>
+        <v>2</v>
       </c>
       <c r="D93">
-        <v>803</v>
+        <v>537</v>
       </c>
       <c r="E93">
-        <v>503</v>
+        <v>446</v>
       </c>
       <c r="F93">
-        <v>5.19</v>
+        <v>0.63</v>
       </c>
       <c r="G93">
-        <v>4.68</v>
+        <v>3.84</v>
       </c>
       <c r="H93">
         <v>1.2</v>
       </c>
       <c r="I93">
-        <v>80.5</v>
+        <v>78.760000000000005</v>
       </c>
     </row>
     <row r="94" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A94">
-        <v>94</v>
+        <v>103</v>
       </c>
       <c r="B94">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="C94">
-        <v>14</v>
+        <v>3</v>
       </c>
       <c r="D94">
-        <v>834</v>
+        <v>560</v>
       </c>
       <c r="E94">
-        <v>503</v>
+        <v>446</v>
       </c>
       <c r="F94">
-        <v>5.59</v>
+        <v>1.05</v>
       </c>
       <c r="G94">
-        <v>4.66</v>
+        <v>3.84</v>
       </c>
       <c r="H94">
         <v>1.2</v>
       </c>
       <c r="I94">
-        <v>79.489999999999995</v>
+        <v>80</v>
       </c>
     </row>
     <row r="95" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A95">
-        <v>95</v>
+        <v>104</v>
       </c>
       <c r="B95">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="C95">
-        <v>15</v>
+        <v>4</v>
       </c>
       <c r="D95">
-        <v>865</v>
+        <v>584</v>
       </c>
       <c r="E95">
-        <v>503</v>
+        <v>446</v>
       </c>
       <c r="F95">
-        <v>5.98</v>
+        <v>1.49</v>
       </c>
       <c r="G95">
-        <v>4.6500000000000004</v>
+        <v>3.84</v>
       </c>
       <c r="H95">
         <v>1.2</v>
       </c>
       <c r="I95">
-        <v>78.7</v>
+        <v>81.62</v>
       </c>
     </row>
     <row r="96" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A96">
-        <v>96</v>
+        <v>105</v>
       </c>
       <c r="B96">
+        <v>6</v>
+      </c>
+      <c r="C96">
         <v>5</v>
       </c>
-      <c r="C96">
-        <v>16</v>
-      </c>
       <c r="D96">
-        <v>896</v>
+        <v>607</v>
       </c>
       <c r="E96">
-        <v>503</v>
+        <v>446</v>
       </c>
       <c r="F96">
-        <v>6.48</v>
+        <v>1.91</v>
       </c>
       <c r="G96">
-        <v>4.71</v>
+        <v>3.84</v>
       </c>
       <c r="H96">
         <v>1.2</v>
       </c>
       <c r="I96">
-        <v>77.95</v>
+        <v>83.55</v>
       </c>
     </row>
     <row r="97" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A97">
-        <v>97</v>
+        <v>106</v>
       </c>
       <c r="B97">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="C97">
-        <v>17</v>
+        <v>6</v>
       </c>
       <c r="D97">
-        <v>927</v>
+        <v>630</v>
       </c>
       <c r="E97">
-        <v>503</v>
+        <v>446</v>
       </c>
       <c r="F97">
-        <v>6.87</v>
+        <v>2.34</v>
       </c>
       <c r="G97">
-        <v>4.71</v>
+        <v>3.84</v>
       </c>
       <c r="H97">
         <v>1.2</v>
       </c>
       <c r="I97">
-        <v>77.2</v>
+        <v>85.41</v>
       </c>
     </row>
     <row r="98" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A98">
-        <v>98</v>
+        <v>107</v>
       </c>
       <c r="B98">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="C98">
-        <v>18</v>
+        <v>7</v>
       </c>
       <c r="D98">
-        <v>958</v>
+        <v>654</v>
       </c>
       <c r="E98">
-        <v>503</v>
+        <v>446</v>
       </c>
       <c r="F98">
-        <v>7.27</v>
+        <v>2.78</v>
       </c>
       <c r="G98">
-        <v>4.71</v>
+        <v>3.84</v>
       </c>
       <c r="H98">
         <v>1.2</v>
       </c>
       <c r="I98">
-        <v>76.56</v>
+        <v>85.67</v>
       </c>
     </row>
     <row r="99" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A99">
-        <v>99</v>
+        <v>108</v>
       </c>
       <c r="B99">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="C99">
-        <v>19</v>
+        <v>8</v>
       </c>
       <c r="D99">
-        <v>989</v>
+        <v>677</v>
       </c>
       <c r="E99">
-        <v>503</v>
+        <v>446</v>
       </c>
       <c r="F99">
-        <v>7.66</v>
+        <v>3.2</v>
       </c>
       <c r="G99">
-        <v>4.71</v>
+        <v>3.84</v>
       </c>
       <c r="H99">
         <v>1.2</v>
       </c>
       <c r="I99">
-        <v>75.86</v>
+        <v>85.17</v>
       </c>
     </row>
     <row r="100" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A100">
-        <v>100</v>
+        <v>109</v>
       </c>
       <c r="B100">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="C100">
-        <v>20</v>
+        <v>9</v>
       </c>
       <c r="D100">
-        <v>1020</v>
+        <v>701</v>
       </c>
       <c r="E100">
-        <v>503</v>
+        <v>446</v>
       </c>
       <c r="F100">
-        <v>8.0500000000000007</v>
+        <v>3.64</v>
       </c>
       <c r="G100">
-        <v>4.7300000000000004</v>
+        <v>3.84</v>
       </c>
       <c r="H100">
         <v>1.2</v>
       </c>
       <c r="I100">
-        <v>75.319999999999993</v>
+        <v>83.96</v>
       </c>
     </row>
     <row r="101" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A101">
-        <v>101</v>
+        <v>110</v>
       </c>
       <c r="B101">
         <v>6</v>
       </c>
       <c r="C101">
-        <v>1</v>
+        <v>10</v>
       </c>
       <c r="D101">
-        <v>432</v>
+        <v>724</v>
       </c>
       <c r="E101">
-        <v>565</v>
+        <v>446</v>
       </c>
       <c r="F101">
-        <v>0.2</v>
+        <v>4.0599999999999996</v>
       </c>
       <c r="G101">
-        <v>3.9</v>
+        <v>3.84</v>
       </c>
       <c r="H101">
         <v>1.2</v>
       </c>
       <c r="I101">
-        <v>7756</v>
+        <v>82.93</v>
       </c>
     </row>
     <row r="102" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A102">
-        <v>102</v>
+        <v>111</v>
       </c>
       <c r="B102">
         <v>6</v>
       </c>
       <c r="C102">
-        <v>2</v>
+        <v>11</v>
       </c>
       <c r="D102">
-        <v>463</v>
+        <v>748</v>
       </c>
       <c r="E102">
-        <v>565</v>
+        <v>446</v>
       </c>
       <c r="F102">
-        <v>0.66</v>
+        <v>4.5</v>
       </c>
       <c r="G102">
-        <v>3.8</v>
+        <v>3.84</v>
       </c>
       <c r="H102">
         <v>1.2</v>
       </c>
       <c r="I102">
-        <v>78.569999999999993</v>
+        <v>81.900000000000006</v>
       </c>
     </row>
     <row r="103" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A103">
-        <v>103</v>
+        <v>112</v>
       </c>
       <c r="B103">
         <v>6</v>
       </c>
       <c r="C103">
-        <v>3</v>
+        <v>12</v>
       </c>
       <c r="D103">
-        <v>494</v>
+        <v>771</v>
       </c>
       <c r="E103">
-        <v>565</v>
+        <v>446</v>
       </c>
       <c r="F103">
-        <v>1.07</v>
+        <v>4.92</v>
       </c>
       <c r="G103">
-        <v>3.81</v>
+        <v>3.84</v>
       </c>
       <c r="H103">
         <v>1.2</v>
       </c>
       <c r="I103">
-        <v>79.7</v>
+        <v>80.91</v>
       </c>
     </row>
     <row r="104" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A104">
-        <v>104</v>
+        <v>113</v>
       </c>
       <c r="B104">
         <v>6</v>
       </c>
       <c r="C104">
-        <v>4</v>
+        <v>13</v>
       </c>
       <c r="D104">
-        <v>525</v>
+        <v>795</v>
       </c>
       <c r="E104">
-        <v>565</v>
+        <v>446</v>
       </c>
       <c r="F104">
-        <v>1.47</v>
+        <v>5.36</v>
       </c>
       <c r="G104">
-        <v>3.81</v>
+        <v>3.84</v>
       </c>
       <c r="H104">
         <v>1.2</v>
       </c>
       <c r="I104">
-        <v>81.099999999999994</v>
+        <v>79.83</v>
       </c>
     </row>
     <row r="105" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A105">
-        <v>105</v>
+        <v>114</v>
       </c>
       <c r="B105">
         <v>6</v>
       </c>
       <c r="C105">
-        <v>5</v>
+        <v>14</v>
       </c>
       <c r="D105">
-        <v>556</v>
+        <v>818</v>
       </c>
       <c r="E105">
-        <v>565</v>
+        <v>446</v>
       </c>
       <c r="F105">
-        <v>1.88</v>
+        <v>5.78</v>
       </c>
       <c r="G105">
-        <v>3.81</v>
+        <v>3.84</v>
       </c>
       <c r="H105">
         <v>1.2</v>
       </c>
       <c r="I105">
-        <v>83.09</v>
+        <v>79.010000000000005</v>
       </c>
     </row>
     <row r="106" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A106">
-        <v>106</v>
+        <v>115</v>
       </c>
       <c r="B106">
         <v>6</v>
       </c>
       <c r="C106">
-        <v>6</v>
+        <v>15</v>
       </c>
       <c r="D106">
-        <v>587</v>
+        <v>842</v>
       </c>
       <c r="E106">
-        <v>565</v>
+        <v>446</v>
       </c>
       <c r="F106">
-        <v>2.2799999999999998</v>
+        <v>6.22</v>
       </c>
       <c r="G106">
-        <v>3.81</v>
+        <v>3.84</v>
       </c>
       <c r="H106">
         <v>1.2</v>
       </c>
       <c r="I106">
-        <v>84.440799999999996</v>
+        <v>78.233999999999995</v>
       </c>
     </row>
     <row r="107" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A107">
-        <v>107</v>
+        <v>116</v>
       </c>
       <c r="B107">
         <v>6</v>
       </c>
       <c r="C107">
-        <v>7</v>
+        <v>16</v>
       </c>
       <c r="D107">
-        <v>618</v>
+        <v>865</v>
       </c>
       <c r="E107">
-        <v>565</v>
+        <v>446</v>
       </c>
       <c r="F107">
-        <v>2.69</v>
+        <v>6.65</v>
       </c>
       <c r="G107">
-        <v>3.8</v>
+        <v>3.84</v>
       </c>
       <c r="H107">
         <v>1.2</v>
       </c>
       <c r="I107">
-        <v>84.930800000000005</v>
+        <v>77.34</v>
       </c>
     </row>
     <row r="108" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A108">
-        <v>108</v>
+        <v>117</v>
       </c>
       <c r="B108">
         <v>6</v>
       </c>
       <c r="C108">
-        <v>8</v>
+        <v>17</v>
       </c>
       <c r="D108">
-        <v>649</v>
+        <v>888</v>
       </c>
       <c r="E108">
-        <v>565</v>
+        <v>446</v>
       </c>
       <c r="F108">
-        <v>3.18</v>
+        <v>7.07</v>
       </c>
       <c r="G108">
-        <v>3.87</v>
+        <v>3.84</v>
       </c>
       <c r="H108">
         <v>1.2</v>
       </c>
       <c r="I108">
-        <v>84.67</v>
+        <v>76.69</v>
       </c>
     </row>
     <row r="109" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A109">
-        <v>109</v>
+        <v>118</v>
       </c>
       <c r="B109">
         <v>6</v>
       </c>
       <c r="C109">
-        <v>9</v>
+        <v>18</v>
       </c>
       <c r="D109">
-        <v>680</v>
+        <v>912</v>
       </c>
       <c r="E109">
-        <v>565</v>
+        <v>446</v>
       </c>
       <c r="F109">
-        <v>3.59</v>
+        <v>7.51</v>
       </c>
       <c r="G109">
-        <v>3.88</v>
+        <v>3.84</v>
       </c>
       <c r="H109">
         <v>1.2</v>
       </c>
       <c r="I109">
-        <v>83.92</v>
+        <v>75.974000000000004</v>
       </c>
     </row>
     <row r="110" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A110">
-        <v>110</v>
+        <v>119</v>
       </c>
       <c r="B110">
         <v>6</v>
       </c>
       <c r="C110">
-        <v>10</v>
+        <v>19</v>
       </c>
       <c r="D110">
-        <v>711</v>
+        <v>935</v>
       </c>
       <c r="E110">
-        <v>565</v>
+        <v>446</v>
       </c>
       <c r="F110">
-        <v>3.99</v>
+        <v>7.93</v>
       </c>
       <c r="G110">
-        <v>3.88</v>
+        <v>3.84</v>
       </c>
       <c r="H110">
         <v>1.2</v>
       </c>
       <c r="I110">
-        <v>83</v>
+        <v>75.400000000000006</v>
       </c>
     </row>
     <row r="111" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A111">
-        <v>111</v>
+        <v>120</v>
       </c>
       <c r="B111">
         <v>6</v>
       </c>
       <c r="C111">
-        <v>11</v>
+        <v>20</v>
       </c>
       <c r="D111">
-        <v>741</v>
+        <v>959</v>
       </c>
       <c r="E111">
-        <v>565</v>
+        <v>446</v>
       </c>
       <c r="F111">
-        <v>4.4000000000000004</v>
+        <v>8.3699999999999992</v>
       </c>
       <c r="G111">
-        <v>3.87</v>
+        <v>3.84</v>
       </c>
       <c r="H111">
         <v>1.2</v>
       </c>
       <c r="I111">
-        <v>82.02</v>
+        <v>74.849999999999994</v>
       </c>
     </row>
     <row r="112" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A112">
-        <v>112</v>
+        <v>121</v>
       </c>
       <c r="B112">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="C112">
-        <v>12</v>
+        <v>1</v>
       </c>
       <c r="D112">
-        <v>772</v>
+        <v>513</v>
       </c>
       <c r="E112">
-        <v>565</v>
+        <v>493</v>
       </c>
       <c r="F112">
-        <v>4.8</v>
+        <v>0.19</v>
       </c>
       <c r="G112">
-        <v>3.84</v>
+        <v>2.98</v>
       </c>
       <c r="H112">
         <v>1.2</v>
       </c>
       <c r="I112">
-        <v>81.03</v>
+        <v>76.89</v>
       </c>
     </row>
     <row r="113" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A113">
-        <v>113</v>
+        <v>122</v>
       </c>
       <c r="B113">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="C113">
-        <v>13</v>
+        <v>2</v>
       </c>
       <c r="D113">
-        <v>803</v>
+        <v>537</v>
       </c>
       <c r="E113">
-        <v>565</v>
+        <v>493</v>
       </c>
       <c r="F113">
-        <v>5.19</v>
+        <v>0.63</v>
       </c>
       <c r="G113">
-        <v>3.85</v>
+        <v>2.98</v>
       </c>
       <c r="H113">
         <v>1.2</v>
       </c>
       <c r="I113">
-        <v>80.13</v>
+        <v>77.98</v>
       </c>
     </row>
     <row r="114" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A114">
-        <v>114</v>
+        <v>123</v>
       </c>
       <c r="B114">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="C114">
-        <v>14</v>
+        <v>3</v>
       </c>
       <c r="D114">
-        <v>834</v>
+        <v>560</v>
       </c>
       <c r="E114">
-        <v>565</v>
+        <v>493</v>
       </c>
       <c r="F114">
-        <v>5.59</v>
+        <v>1.05</v>
       </c>
       <c r="G114">
-        <v>3.85</v>
+        <v>2.98</v>
       </c>
       <c r="H114">
         <v>1.2</v>
       </c>
       <c r="I114">
-        <v>79.16</v>
+        <v>78.924000000000007</v>
       </c>
     </row>
     <row r="115" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A115">
-        <v>115</v>
+        <v>124</v>
       </c>
       <c r="B115">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="C115">
-        <v>15</v>
+        <v>4</v>
       </c>
       <c r="D115">
-        <v>865</v>
+        <v>584</v>
       </c>
       <c r="E115">
-        <v>565</v>
+        <v>493</v>
       </c>
       <c r="F115">
-        <v>5.98</v>
+        <v>1.49</v>
       </c>
       <c r="G115">
-        <v>3.85</v>
+        <v>2.98</v>
       </c>
       <c r="H115">
         <v>1.2</v>
       </c>
       <c r="I115">
-        <v>78.290000000000006</v>
+        <v>80.05</v>
       </c>
     </row>
     <row r="116" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A116">
-        <v>116</v>
+        <v>125</v>
       </c>
       <c r="B116">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="C116">
-        <v>16</v>
+        <v>5</v>
       </c>
       <c r="D116">
-        <v>896</v>
+        <v>607</v>
       </c>
       <c r="E116">
-        <v>565</v>
+        <v>493</v>
       </c>
       <c r="F116">
-        <v>6.38</v>
+        <v>1.91</v>
       </c>
       <c r="G116">
-        <v>3.85</v>
+        <v>2.98</v>
       </c>
       <c r="H116">
         <v>1.2</v>
       </c>
       <c r="I116">
-        <v>7759</v>
+        <v>81.33</v>
       </c>
     </row>
     <row r="117" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A117">
-        <v>117</v>
+        <v>126</v>
       </c>
       <c r="B117">
+        <v>7</v>
+      </c>
+      <c r="C117">
         <v>6</v>
       </c>
-      <c r="C117">
-        <v>17</v>
-      </c>
       <c r="D117">
-        <v>927</v>
+        <v>630</v>
       </c>
       <c r="E117">
-        <v>565</v>
+        <v>493</v>
       </c>
       <c r="F117">
-        <v>6.87</v>
+        <v>2.34</v>
       </c>
       <c r="G117">
-        <v>3.91</v>
+        <v>2.98</v>
       </c>
       <c r="H117">
         <v>1.2</v>
       </c>
       <c r="I117">
-        <v>76.930000000000007</v>
+        <v>82.45</v>
       </c>
     </row>
     <row r="118" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A118">
-        <v>118</v>
+        <v>127</v>
       </c>
       <c r="B118">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="C118">
-        <v>18</v>
+        <v>7</v>
       </c>
       <c r="D118">
-        <v>958</v>
+        <v>654</v>
       </c>
       <c r="E118">
-        <v>565</v>
+        <v>493</v>
       </c>
       <c r="F118">
-        <v>7.27</v>
+        <v>2.78</v>
       </c>
       <c r="G118">
-        <v>3.91</v>
+        <v>2.98</v>
       </c>
       <c r="H118">
         <v>1.2</v>
       </c>
       <c r="I118">
-        <v>76.31</v>
+        <v>82.89</v>
       </c>
     </row>
     <row r="119" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A119">
-        <v>119</v>
+        <v>128</v>
       </c>
       <c r="B119">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="C119">
-        <v>19</v>
+        <v>8</v>
       </c>
       <c r="D119">
-        <v>989</v>
+        <v>677</v>
       </c>
       <c r="E119">
-        <v>565</v>
+        <v>493</v>
       </c>
       <c r="F119">
-        <v>7.65</v>
+        <v>3.2</v>
       </c>
       <c r="G119">
-        <v>3.91</v>
+        <v>2.98</v>
       </c>
       <c r="H119">
         <v>1.2</v>
       </c>
       <c r="I119">
-        <v>75.650000000000006</v>
+        <v>82.8</v>
       </c>
     </row>
     <row r="120" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A120">
-        <v>120</v>
+        <v>129</v>
       </c>
       <c r="B120">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="C120">
-        <v>20</v>
+        <v>9</v>
       </c>
       <c r="D120">
-        <v>1020</v>
+        <v>701</v>
       </c>
       <c r="E120">
-        <v>565</v>
+        <v>493</v>
       </c>
       <c r="F120">
-        <v>8.15</v>
+        <v>3.64</v>
       </c>
       <c r="G120">
-        <v>3.86</v>
+        <v>2.98</v>
       </c>
       <c r="H120">
         <v>1.2</v>
       </c>
       <c r="I120">
-        <v>75.099999999999994</v>
+        <v>82.33</v>
       </c>
     </row>
     <row r="121" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A121">
-        <v>121</v>
+        <v>130</v>
       </c>
       <c r="B121">
         <v>7</v>
       </c>
       <c r="C121">
-        <v>1</v>
+        <v>10</v>
       </c>
       <c r="D121">
-        <v>432</v>
+        <v>724</v>
       </c>
       <c r="E121">
-        <v>628</v>
+        <v>493</v>
       </c>
       <c r="F121">
-        <v>0.25</v>
+        <v>4.0599999999999996</v>
       </c>
       <c r="G121">
         <v>2.98</v>
@@ -3901,27 +3916,27 @@
         <v>1.2</v>
       </c>
       <c r="I121">
-        <v>76.62</v>
+        <v>81.61</v>
       </c>
     </row>
     <row r="122" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A122">
-        <v>122</v>
+        <v>131</v>
       </c>
       <c r="B122">
         <v>7</v>
       </c>
       <c r="C122">
-        <v>2</v>
+        <v>11</v>
       </c>
       <c r="D122">
-        <v>463</v>
+        <v>748</v>
       </c>
       <c r="E122">
-        <v>628</v>
+        <v>493</v>
       </c>
       <c r="F122">
-        <v>0.66</v>
+        <v>4.5</v>
       </c>
       <c r="G122">
         <v>2.98</v>
@@ -3930,27 +3945,27 @@
         <v>1.2</v>
       </c>
       <c r="I122">
-        <v>737</v>
+        <v>80.81</v>
       </c>
     </row>
     <row r="123" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A123">
-        <v>123</v>
+        <v>132</v>
       </c>
       <c r="B123">
         <v>7</v>
       </c>
       <c r="C123">
-        <v>3</v>
+        <v>12</v>
       </c>
       <c r="D123">
-        <v>494</v>
+        <v>771</v>
       </c>
       <c r="E123">
-        <v>628</v>
+        <v>493</v>
       </c>
       <c r="F123">
-        <v>1.06</v>
+        <v>4.92</v>
       </c>
       <c r="G123">
         <v>2.98</v>
@@ -3959,2243 +3974,1809 @@
         <v>1.2</v>
       </c>
       <c r="I123">
-        <v>78.209999999999994</v>
+        <v>80.010000000000005</v>
       </c>
     </row>
     <row r="124" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A124">
-        <v>124</v>
+        <v>133</v>
       </c>
       <c r="B124">
         <v>7</v>
       </c>
       <c r="C124">
-        <v>4</v>
+        <v>13</v>
       </c>
       <c r="D124">
-        <v>525</v>
+        <v>795</v>
       </c>
       <c r="E124">
-        <v>628</v>
+        <v>493</v>
       </c>
       <c r="F124">
-        <v>1.47</v>
+        <v>5.36</v>
       </c>
       <c r="G124">
-        <v>2.99</v>
+        <v>2.98</v>
       </c>
       <c r="H124">
         <v>1.2</v>
       </c>
       <c r="I124">
-        <v>79.17</v>
+        <v>78.974000000000004</v>
       </c>
     </row>
     <row r="125" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A125">
-        <v>125</v>
+        <v>134</v>
       </c>
       <c r="B125">
         <v>7</v>
       </c>
       <c r="C125">
-        <v>5</v>
+        <v>14</v>
       </c>
       <c r="D125">
-        <v>556</v>
+        <v>818</v>
       </c>
       <c r="E125">
-        <v>628</v>
+        <v>493</v>
       </c>
       <c r="F125">
-        <v>1.88</v>
+        <v>5.78</v>
       </c>
       <c r="G125">
-        <v>2.99</v>
+        <v>2.98</v>
       </c>
       <c r="H125">
         <v>1.2</v>
       </c>
       <c r="I125">
-        <v>80.430000000000007</v>
+        <v>78.25</v>
       </c>
     </row>
     <row r="126" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A126">
-        <v>126</v>
+        <v>136</v>
       </c>
       <c r="B126">
         <v>7</v>
       </c>
       <c r="C126">
-        <v>6</v>
+        <v>16</v>
       </c>
       <c r="D126">
-        <v>587</v>
+        <v>865</v>
       </c>
       <c r="E126">
-        <v>628</v>
+        <v>493</v>
       </c>
       <c r="F126">
-        <v>2.29</v>
+        <v>6.65</v>
       </c>
       <c r="G126">
-        <v>2.99</v>
+        <v>2.98</v>
       </c>
       <c r="H126">
         <v>1.2</v>
       </c>
       <c r="I126">
-        <v>81.37</v>
+        <v>76.849999999999994</v>
       </c>
     </row>
     <row r="127" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A127">
-        <v>127</v>
+        <v>137</v>
       </c>
       <c r="B127">
         <v>7</v>
       </c>
       <c r="C127">
-        <v>7</v>
+        <v>17</v>
       </c>
       <c r="D127">
-        <v>618</v>
+        <v>888</v>
       </c>
       <c r="E127">
-        <v>628</v>
+        <v>493</v>
       </c>
       <c r="F127">
-        <v>2.69</v>
+        <v>7.07</v>
       </c>
       <c r="G127">
-        <v>2.99</v>
+        <v>2.98</v>
       </c>
       <c r="H127">
         <v>1.2</v>
       </c>
       <c r="I127">
-        <v>81.92</v>
+        <v>76.260000000000005</v>
       </c>
     </row>
     <row r="128" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A128">
-        <v>128</v>
+        <v>138</v>
       </c>
       <c r="B128">
         <v>7</v>
       </c>
       <c r="C128">
-        <v>8</v>
+        <v>18</v>
       </c>
       <c r="D128">
-        <v>649</v>
+        <v>912</v>
       </c>
       <c r="E128">
-        <v>628</v>
+        <v>493</v>
       </c>
       <c r="F128">
-        <v>3.09</v>
+        <v>7.51</v>
       </c>
       <c r="G128">
-        <v>3</v>
+        <v>2.98</v>
       </c>
       <c r="H128">
         <v>1.2</v>
       </c>
       <c r="I128">
-        <v>81.790000000000006</v>
+        <v>75.7</v>
       </c>
     </row>
     <row r="129" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A129">
-        <v>129</v>
+        <v>139</v>
       </c>
       <c r="B129">
         <v>7</v>
       </c>
       <c r="C129">
-        <v>9</v>
+        <v>19</v>
       </c>
       <c r="D129">
-        <v>680</v>
+        <v>935</v>
       </c>
       <c r="E129">
-        <v>628</v>
+        <v>493</v>
       </c>
       <c r="F129">
-        <v>3.49</v>
+        <v>7.93</v>
       </c>
       <c r="G129">
-        <v>3</v>
+        <v>2.98</v>
       </c>
       <c r="H129">
         <v>1.2</v>
       </c>
       <c r="I129">
-        <v>81.489999999999995</v>
+        <v>75</v>
       </c>
     </row>
     <row r="130" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A130">
-        <v>130</v>
+        <v>140</v>
       </c>
       <c r="B130">
         <v>7</v>
       </c>
       <c r="C130">
-        <v>10</v>
+        <v>20</v>
       </c>
       <c r="D130">
-        <v>711</v>
+        <v>959</v>
       </c>
       <c r="E130">
-        <v>628</v>
+        <v>493</v>
       </c>
       <c r="F130">
-        <v>3.99</v>
+        <v>8.3699999999999992</v>
       </c>
       <c r="G130">
-        <v>3.06</v>
+        <v>2.98</v>
       </c>
       <c r="H130">
         <v>1.2</v>
       </c>
       <c r="I130">
-        <v>80.98</v>
+        <v>74.489999999999995</v>
       </c>
     </row>
     <row r="131" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A131">
-        <v>131</v>
+        <v>141</v>
       </c>
       <c r="B131">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="C131">
-        <v>11</v>
+        <v>1</v>
       </c>
       <c r="D131">
-        <v>741</v>
+        <v>513</v>
       </c>
       <c r="E131">
-        <v>628</v>
+        <v>540</v>
       </c>
       <c r="F131">
-        <v>4.4000000000000004</v>
+        <v>0.19</v>
       </c>
       <c r="G131">
-        <v>3.06</v>
+        <v>2.11</v>
       </c>
       <c r="H131">
         <v>1.2</v>
       </c>
       <c r="I131">
-        <v>80.349999999999994</v>
+        <v>75.599999999999994</v>
       </c>
     </row>
     <row r="132" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A132">
-        <v>132</v>
+        <v>142</v>
       </c>
       <c r="B132">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="C132">
-        <v>12</v>
+        <v>2</v>
       </c>
       <c r="D132">
-        <v>772</v>
+        <v>537</v>
       </c>
       <c r="E132">
-        <v>628</v>
+        <v>540</v>
       </c>
       <c r="F132">
-        <v>4.8</v>
+        <v>0.63</v>
       </c>
       <c r="G132">
-        <v>3.06</v>
+        <v>2.11</v>
       </c>
       <c r="H132">
         <v>1.2</v>
       </c>
       <c r="I132">
-        <v>79.67</v>
+        <v>76.3</v>
       </c>
     </row>
     <row r="133" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A133">
-        <v>133</v>
+        <v>143</v>
       </c>
       <c r="B133">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="C133">
-        <v>13</v>
+        <v>3</v>
       </c>
       <c r="D133">
-        <v>803</v>
+        <v>560</v>
       </c>
       <c r="E133">
-        <v>628</v>
+        <v>540</v>
       </c>
       <c r="F133">
-        <v>5.2</v>
+        <v>1.05</v>
       </c>
       <c r="G133">
-        <v>3.05</v>
+        <v>2.11</v>
       </c>
       <c r="H133">
         <v>1.2</v>
       </c>
       <c r="I133">
-        <v>78.97</v>
+        <v>76.989999999999995</v>
       </c>
     </row>
     <row r="134" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A134">
-        <v>134</v>
+        <v>145</v>
       </c>
       <c r="B134">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="C134">
-        <v>14</v>
+        <v>5</v>
       </c>
       <c r="D134">
-        <v>834</v>
+        <v>607</v>
       </c>
       <c r="E134">
-        <v>628</v>
+        <v>540</v>
       </c>
       <c r="F134">
-        <v>5.6</v>
+        <v>1.91</v>
       </c>
       <c r="G134">
-        <v>3.05</v>
+        <v>2.11</v>
       </c>
       <c r="H134">
         <v>1.2</v>
       </c>
       <c r="I134">
-        <v>78.180000000000007</v>
+        <v>78.58</v>
       </c>
     </row>
     <row r="135" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A135">
-        <v>135</v>
+        <v>146</v>
       </c>
       <c r="B135">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="C135">
-        <v>15</v>
+        <v>6</v>
       </c>
       <c r="D135">
-        <v>865</v>
+        <v>630</v>
       </c>
       <c r="E135">
-        <v>628</v>
+        <v>540</v>
       </c>
       <c r="F135">
-        <v>6</v>
+        <v>2.34</v>
       </c>
       <c r="G135">
-        <v>3.05</v>
+        <v>2.11</v>
       </c>
       <c r="H135">
         <v>1.2</v>
       </c>
       <c r="I135">
-        <v>77540</v>
+        <v>79.274000000000001</v>
       </c>
     </row>
     <row r="136" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A136">
-        <v>136</v>
+        <v>147</v>
       </c>
       <c r="B136">
+        <v>8</v>
+      </c>
+      <c r="C136">
         <v>7</v>
       </c>
-      <c r="C136">
-        <v>16</v>
-      </c>
       <c r="D136">
-        <v>896</v>
+        <v>654</v>
       </c>
       <c r="E136">
-        <v>628</v>
+        <v>540</v>
       </c>
       <c r="F136">
-        <v>6.39</v>
+        <v>2.78</v>
       </c>
       <c r="G136">
-        <v>3.05</v>
+        <v>2.11</v>
       </c>
       <c r="H136">
         <v>1.2</v>
       </c>
       <c r="I136">
-        <v>76.92</v>
+        <v>79.709999999999994</v>
       </c>
     </row>
     <row r="137" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A137">
-        <v>137</v>
+        <v>148</v>
       </c>
       <c r="B137">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="C137">
-        <v>17</v>
+        <v>8</v>
       </c>
       <c r="D137">
-        <v>927</v>
+        <v>677</v>
       </c>
       <c r="E137">
-        <v>628</v>
+        <v>540</v>
       </c>
       <c r="F137">
-        <v>6.87</v>
+        <v>3.2</v>
       </c>
       <c r="G137">
-        <v>2.99</v>
+        <v>2.11</v>
       </c>
       <c r="H137">
         <v>1.2</v>
       </c>
       <c r="I137">
-        <v>76.36</v>
+        <v>79.86</v>
       </c>
     </row>
     <row r="138" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A138">
-        <v>138</v>
+        <v>149</v>
       </c>
       <c r="B138">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="C138">
-        <v>18</v>
+        <v>9</v>
       </c>
       <c r="D138">
-        <v>958</v>
+        <v>701</v>
       </c>
       <c r="E138">
-        <v>628</v>
+        <v>540</v>
       </c>
       <c r="F138">
-        <v>7.26</v>
+        <v>3.64</v>
       </c>
       <c r="G138">
-        <v>2.99</v>
+        <v>2.11</v>
       </c>
       <c r="H138">
         <v>1.2</v>
       </c>
       <c r="I138">
-        <v>75.72</v>
+        <v>79.8</v>
       </c>
     </row>
     <row r="139" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A139">
-        <v>139</v>
+        <v>150</v>
       </c>
       <c r="B139">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="C139">
-        <v>19</v>
+        <v>10</v>
       </c>
       <c r="D139">
-        <v>989</v>
+        <v>724</v>
       </c>
       <c r="E139">
-        <v>628</v>
+        <v>540</v>
       </c>
       <c r="F139">
-        <v>7.65</v>
+        <v>4.0599999999999996</v>
       </c>
       <c r="G139">
-        <v>2.99</v>
+        <v>2.11</v>
       </c>
       <c r="H139">
         <v>1.2</v>
       </c>
       <c r="I139">
-        <v>75.19</v>
+        <v>79.239999999999995</v>
       </c>
     </row>
     <row r="140" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A140">
-        <v>140</v>
+        <v>151</v>
       </c>
       <c r="B140">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="C140">
-        <v>20</v>
+        <v>11</v>
       </c>
       <c r="D140">
-        <v>1020</v>
+        <v>748</v>
       </c>
       <c r="E140">
-        <v>628</v>
+        <v>540</v>
       </c>
       <c r="F140">
-        <v>8.0500000000000007</v>
+        <v>4.5</v>
       </c>
       <c r="G140">
-        <v>2.99</v>
+        <v>2.11</v>
       </c>
       <c r="H140">
         <v>1.2</v>
       </c>
       <c r="I140">
-        <v>74.680000000000007</v>
+        <v>78.81</v>
       </c>
     </row>
     <row r="141" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A141">
-        <v>141</v>
+        <v>152</v>
       </c>
       <c r="B141">
         <v>8</v>
       </c>
       <c r="C141">
-        <v>1</v>
+        <v>12</v>
       </c>
       <c r="D141">
-        <v>432</v>
+        <v>771</v>
       </c>
       <c r="E141">
-        <v>691</v>
+        <v>540</v>
       </c>
       <c r="F141">
-        <v>0.25</v>
+        <v>4.92</v>
       </c>
       <c r="G141">
-        <v>2.16</v>
+        <v>2.11</v>
       </c>
       <c r="H141">
         <v>1.2</v>
       </c>
       <c r="I141">
-        <v>74.92</v>
+        <v>78.38</v>
       </c>
     </row>
     <row r="142" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A142">
-        <v>142</v>
+        <v>154</v>
       </c>
       <c r="B142">
         <v>8</v>
       </c>
       <c r="C142">
-        <v>2</v>
+        <v>14</v>
       </c>
       <c r="D142">
-        <v>463</v>
+        <v>818</v>
       </c>
       <c r="E142">
-        <v>691</v>
+        <v>540</v>
       </c>
       <c r="F142">
-        <v>0.66</v>
+        <v>5.78</v>
       </c>
       <c r="G142">
-        <v>2.16</v>
+        <v>2.11</v>
       </c>
       <c r="H142">
         <v>1.2</v>
       </c>
       <c r="I142">
-        <v>75.61</v>
+        <v>77.209999999999994</v>
       </c>
     </row>
     <row r="143" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A143">
-        <v>143</v>
+        <v>155</v>
       </c>
       <c r="B143">
         <v>8</v>
       </c>
       <c r="C143">
-        <v>3</v>
+        <v>15</v>
       </c>
       <c r="D143">
-        <v>494</v>
+        <v>842</v>
       </c>
       <c r="E143">
-        <v>691</v>
+        <v>540</v>
       </c>
       <c r="F143">
-        <v>1.07</v>
+        <v>6.22</v>
       </c>
       <c r="G143">
-        <v>2.16</v>
+        <v>2.11</v>
       </c>
       <c r="H143">
         <v>1.2</v>
       </c>
       <c r="I143">
-        <v>76.23</v>
+        <v>76.674000000000007</v>
       </c>
     </row>
     <row r="144" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A144">
-        <v>144</v>
+        <v>156</v>
       </c>
       <c r="B144">
         <v>8</v>
       </c>
       <c r="C144">
-        <v>4</v>
+        <v>16</v>
       </c>
       <c r="D144">
-        <v>525</v>
+        <v>865</v>
       </c>
       <c r="E144">
-        <v>691</v>
+        <v>540</v>
       </c>
       <c r="F144">
-        <v>1.48</v>
+        <v>6.65</v>
       </c>
       <c r="G144">
-        <v>2.17</v>
+        <v>2.11</v>
       </c>
       <c r="H144">
         <v>1.2</v>
       </c>
       <c r="I144">
-        <v>76.900000000000006</v>
+        <v>75.974000000000004</v>
       </c>
     </row>
     <row r="145" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A145">
-        <v>145</v>
+        <v>157</v>
       </c>
       <c r="B145">
         <v>8</v>
       </c>
       <c r="C145">
-        <v>5</v>
+        <v>17</v>
       </c>
       <c r="D145">
-        <v>556</v>
+        <v>888</v>
       </c>
       <c r="E145">
-        <v>691</v>
+        <v>540</v>
       </c>
       <c r="F145">
-        <v>1.88</v>
+        <v>7.07</v>
       </c>
       <c r="G145">
-        <v>2.17</v>
+        <v>2.11</v>
       </c>
       <c r="H145">
         <v>1.2</v>
       </c>
       <c r="I145">
-        <v>77740</v>
+        <v>77.36</v>
       </c>
     </row>
     <row r="146" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A146">
-        <v>146</v>
+        <v>158</v>
       </c>
       <c r="B146">
         <v>8</v>
       </c>
       <c r="C146">
-        <v>6</v>
+        <v>18</v>
       </c>
       <c r="D146">
-        <v>587</v>
+        <v>912</v>
       </c>
       <c r="E146">
-        <v>691</v>
+        <v>540</v>
       </c>
       <c r="F146">
-        <v>2.29</v>
+        <v>7.51</v>
       </c>
       <c r="G146">
-        <v>2.17</v>
+        <v>2.11</v>
       </c>
       <c r="H146">
         <v>1.2</v>
       </c>
       <c r="I146">
-        <v>78.38</v>
+        <v>74.95</v>
       </c>
     </row>
     <row r="147" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A147">
-        <v>147</v>
+        <v>159</v>
       </c>
       <c r="B147">
         <v>8</v>
       </c>
       <c r="C147">
-        <v>7</v>
+        <v>19</v>
       </c>
       <c r="D147">
-        <v>618</v>
+        <v>935</v>
       </c>
       <c r="E147">
-        <v>691</v>
+        <v>540</v>
       </c>
       <c r="F147">
-        <v>2.7</v>
+        <v>7.93</v>
       </c>
       <c r="G147">
-        <v>2.17</v>
+        <v>2.11</v>
       </c>
       <c r="H147">
         <v>1.2</v>
       </c>
       <c r="I147">
-        <v>78.680000000000007</v>
+        <v>74.510000000000005</v>
       </c>
     </row>
     <row r="148" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A148">
-        <v>148</v>
+        <v>160</v>
       </c>
       <c r="B148">
         <v>8</v>
       </c>
       <c r="C148">
-        <v>8</v>
+        <v>20</v>
       </c>
       <c r="D148">
-        <v>649</v>
+        <v>959</v>
       </c>
       <c r="E148">
-        <v>691</v>
+        <v>540</v>
       </c>
       <c r="F148">
-        <v>3.1</v>
+        <v>8.3699999999999992</v>
       </c>
       <c r="G148">
-        <v>2.17</v>
+        <v>2.11</v>
       </c>
       <c r="H148">
         <v>1.2</v>
       </c>
       <c r="I148">
-        <v>78.89</v>
+        <v>73.94</v>
       </c>
     </row>
     <row r="149" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A149">
-        <v>149</v>
+        <v>161</v>
       </c>
       <c r="B149">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="C149">
-        <v>9</v>
+        <v>1</v>
       </c>
       <c r="D149">
-        <v>680</v>
+        <v>513</v>
       </c>
       <c r="E149">
-        <v>691</v>
+        <v>586</v>
       </c>
       <c r="F149">
-        <v>3.49</v>
+        <v>0.19</v>
       </c>
       <c r="G149">
-        <v>2.1800000000000002</v>
+        <v>1.27</v>
       </c>
       <c r="H149">
         <v>1.2</v>
       </c>
       <c r="I149">
-        <v>78.92</v>
+        <v>73.900000000000006</v>
       </c>
     </row>
     <row r="150" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A150">
-        <v>150</v>
+        <v>162</v>
       </c>
       <c r="B150">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="C150">
-        <v>10</v>
+        <v>2</v>
       </c>
       <c r="D150">
-        <v>711</v>
+        <v>537</v>
       </c>
       <c r="E150">
-        <v>691</v>
+        <v>586</v>
       </c>
       <c r="F150">
-        <v>3.9</v>
+        <v>0.63</v>
       </c>
       <c r="G150">
-        <v>2.1800000000000002</v>
+        <v>1.27</v>
       </c>
       <c r="H150">
         <v>1.2</v>
       </c>
       <c r="I150">
-        <v>78.72</v>
+        <v>74.274000000000001</v>
       </c>
     </row>
     <row r="151" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A151">
-        <v>151</v>
+        <v>163</v>
       </c>
       <c r="B151">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="C151">
-        <v>11</v>
+        <v>3</v>
       </c>
       <c r="D151">
-        <v>741</v>
+        <v>560</v>
       </c>
       <c r="E151">
-        <v>691</v>
+        <v>586</v>
       </c>
       <c r="F151">
-        <v>4.3</v>
+        <v>1.05</v>
       </c>
       <c r="G151">
-        <v>2.19</v>
+        <v>1.27</v>
       </c>
       <c r="H151">
         <v>1.2</v>
       </c>
       <c r="I151">
-        <v>78.400000000000006</v>
+        <v>74.760000000000005</v>
       </c>
     </row>
     <row r="152" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A152">
-        <v>152</v>
+        <v>164</v>
       </c>
       <c r="B152">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="C152">
-        <v>12</v>
+        <v>4</v>
       </c>
       <c r="D152">
-        <v>772</v>
+        <v>584</v>
       </c>
       <c r="E152">
-        <v>691</v>
+        <v>586</v>
       </c>
       <c r="F152">
-        <v>4.79</v>
+        <v>1.49</v>
       </c>
       <c r="G152">
-        <v>2.16</v>
+        <v>1.27</v>
       </c>
       <c r="H152">
         <v>1.2</v>
       </c>
       <c r="I152">
-        <v>78.069999999999993</v>
+        <v>75.3</v>
       </c>
     </row>
     <row r="153" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A153">
-        <v>153</v>
+        <v>165</v>
       </c>
       <c r="B153">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="C153">
-        <v>13</v>
+        <v>5</v>
       </c>
       <c r="D153">
-        <v>803</v>
+        <v>607</v>
       </c>
       <c r="E153">
-        <v>691</v>
+        <v>586</v>
       </c>
       <c r="F153">
-        <v>5.2</v>
+        <v>1.91</v>
       </c>
       <c r="G153">
-        <v>2.17</v>
+        <v>1.27</v>
       </c>
       <c r="H153">
         <v>1.2</v>
       </c>
       <c r="I153">
-        <v>77.610799999999998</v>
+        <v>75.849999999999994</v>
       </c>
     </row>
     <row r="154" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A154">
-        <v>154</v>
+        <v>166</v>
       </c>
       <c r="B154">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="C154">
-        <v>14</v>
+        <v>6</v>
       </c>
       <c r="D154">
-        <v>834</v>
+        <v>630</v>
       </c>
       <c r="E154">
-        <v>691</v>
+        <v>586</v>
       </c>
       <c r="F154">
-        <v>5.61</v>
+        <v>2.34</v>
       </c>
       <c r="G154">
-        <v>2.14</v>
+        <v>1.27</v>
       </c>
       <c r="H154">
         <v>1.2</v>
       </c>
       <c r="I154">
-        <v>77.06</v>
+        <v>76.650000000000006</v>
       </c>
     </row>
     <row r="155" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A155">
-        <v>155</v>
+        <v>167</v>
       </c>
       <c r="B155">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="C155">
-        <v>15</v>
+        <v>7</v>
       </c>
       <c r="D155">
-        <v>865</v>
+        <v>654</v>
       </c>
       <c r="E155">
-        <v>691</v>
+        <v>586</v>
       </c>
       <c r="F155">
-        <v>6.01</v>
+        <v>2.78</v>
       </c>
       <c r="G155">
-        <v>2.14</v>
+        <v>1.27</v>
       </c>
       <c r="H155">
         <v>1.2</v>
       </c>
       <c r="I155">
-        <v>76.489999999999995</v>
+        <v>77.034000000000006</v>
       </c>
     </row>
     <row r="156" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A156">
-        <v>156</v>
+        <v>168</v>
       </c>
       <c r="B156">
+        <v>9</v>
+      </c>
+      <c r="C156">
         <v>8</v>
       </c>
-      <c r="C156">
-        <v>16</v>
-      </c>
       <c r="D156">
-        <v>896</v>
+        <v>677</v>
       </c>
       <c r="E156">
-        <v>691</v>
+        <v>586</v>
       </c>
       <c r="F156">
-        <v>6.39</v>
+        <v>3.2</v>
       </c>
       <c r="G156">
-        <v>2.15</v>
+        <v>1.27</v>
       </c>
       <c r="H156">
         <v>1.2</v>
       </c>
       <c r="I156">
-        <v>76.010000000000005</v>
+        <v>77.260000000000005</v>
       </c>
     </row>
     <row r="157" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A157">
-        <v>157</v>
+        <v>169</v>
       </c>
       <c r="B157">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="C157">
-        <v>17</v>
+        <v>9</v>
       </c>
       <c r="D157">
-        <v>927</v>
+        <v>701</v>
       </c>
       <c r="E157">
-        <v>691</v>
+        <v>586</v>
       </c>
       <c r="F157">
-        <v>6.88</v>
+        <v>3.64</v>
       </c>
       <c r="G157">
-        <v>2.21</v>
+        <v>1.27</v>
       </c>
       <c r="H157">
         <v>1.2</v>
       </c>
       <c r="I157">
-        <v>75.44</v>
+        <v>77.319999999999993</v>
       </c>
     </row>
     <row r="158" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A158">
-        <v>158</v>
+        <v>170</v>
       </c>
       <c r="B158">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="C158">
-        <v>18</v>
+        <v>10</v>
       </c>
       <c r="D158">
-        <v>958</v>
+        <v>724</v>
       </c>
       <c r="E158">
-        <v>691</v>
+        <v>586</v>
       </c>
       <c r="F158">
-        <v>7.26</v>
+        <v>4.0599999999999996</v>
       </c>
       <c r="G158">
-        <v>2.21</v>
+        <v>1.27</v>
       </c>
       <c r="H158">
         <v>1.2</v>
       </c>
       <c r="I158">
-        <v>74.98</v>
+        <v>77.25</v>
       </c>
     </row>
     <row r="159" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A159">
-        <v>159</v>
+        <v>171</v>
       </c>
       <c r="B159">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="C159">
-        <v>19</v>
+        <v>11</v>
       </c>
       <c r="D159">
-        <v>989</v>
+        <v>748</v>
       </c>
       <c r="E159">
-        <v>691</v>
+        <v>586</v>
       </c>
       <c r="F159">
-        <v>7.72</v>
+        <v>4.5</v>
       </c>
       <c r="G159">
-        <v>2.17</v>
+        <v>1.27</v>
       </c>
       <c r="H159">
         <v>1.2</v>
       </c>
       <c r="I159">
-        <v>74.5</v>
+        <v>76.849999999999994</v>
       </c>
     </row>
     <row r="160" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A160">
-        <v>160</v>
+        <v>172</v>
       </c>
       <c r="B160">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="C160">
-        <v>20</v>
+        <v>12</v>
       </c>
       <c r="D160">
-        <v>1020</v>
+        <v>771</v>
       </c>
       <c r="E160">
-        <v>691</v>
+        <v>586</v>
       </c>
       <c r="F160">
-        <v>8.09</v>
+        <v>4.92</v>
       </c>
       <c r="G160">
-        <v>2.17</v>
+        <v>1.27</v>
       </c>
       <c r="H160">
         <v>1.2</v>
       </c>
       <c r="I160">
-        <v>74.02</v>
+        <v>76.724000000000004</v>
       </c>
     </row>
     <row r="161" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A161">
-        <v>161</v>
+        <v>173</v>
       </c>
       <c r="B161">
         <v>9</v>
       </c>
       <c r="C161">
-        <v>1</v>
+        <v>13</v>
       </c>
       <c r="D161">
-        <v>432</v>
+        <v>795</v>
       </c>
       <c r="E161">
-        <v>754</v>
+        <v>586</v>
       </c>
       <c r="F161">
-        <v>0.26</v>
+        <v>5.36</v>
       </c>
       <c r="G161">
-        <v>1.36</v>
+        <v>1.27</v>
       </c>
       <c r="H161">
         <v>1.2</v>
       </c>
       <c r="I161">
-        <v>73.25</v>
+        <v>76.174000000000007</v>
       </c>
     </row>
     <row r="162" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A162">
-        <v>162</v>
+        <v>174</v>
       </c>
       <c r="B162">
         <v>9</v>
       </c>
       <c r="C162">
-        <v>2</v>
+        <v>14</v>
       </c>
       <c r="D162">
-        <v>463</v>
+        <v>818</v>
       </c>
       <c r="E162">
-        <v>754</v>
+        <v>586</v>
       </c>
       <c r="F162">
-        <v>0.66</v>
+        <v>5.78</v>
       </c>
       <c r="G162">
-        <v>1.34</v>
+        <v>1.27</v>
       </c>
       <c r="H162">
         <v>1.2</v>
       </c>
       <c r="I162">
-        <v>73.72</v>
+        <v>75.8</v>
       </c>
     </row>
     <row r="163" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A163">
-        <v>163</v>
+        <v>175</v>
       </c>
       <c r="B163">
         <v>9</v>
       </c>
       <c r="C163">
-        <v>3</v>
+        <v>15</v>
       </c>
       <c r="D163">
-        <v>494</v>
+        <v>842</v>
       </c>
       <c r="E163">
-        <v>754</v>
+        <v>586</v>
       </c>
       <c r="F163">
-        <v>1.07</v>
+        <v>6.22</v>
       </c>
       <c r="G163">
-        <v>1.34</v>
+        <v>1.27</v>
       </c>
       <c r="H163">
         <v>1.2</v>
       </c>
       <c r="I163">
-        <v>74.180000000000007</v>
+        <v>75.42</v>
       </c>
     </row>
     <row r="164" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A164">
-        <v>164</v>
+        <v>176</v>
       </c>
       <c r="B164">
         <v>9</v>
       </c>
       <c r="C164">
-        <v>4</v>
+        <v>16</v>
       </c>
       <c r="D164">
-        <v>525</v>
+        <v>865</v>
       </c>
       <c r="E164">
-        <v>754</v>
+        <v>586</v>
       </c>
       <c r="F164">
-        <v>1.47</v>
+        <v>6.65</v>
       </c>
       <c r="G164">
-        <v>1.34</v>
+        <v>1.27</v>
       </c>
       <c r="H164">
         <v>1.2</v>
       </c>
       <c r="I164">
-        <v>7459</v>
+        <v>74.989999999999995</v>
       </c>
     </row>
     <row r="165" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A165">
-        <v>165</v>
+        <v>177</v>
       </c>
       <c r="B165">
         <v>9</v>
       </c>
       <c r="C165">
-        <v>5</v>
+        <v>17</v>
       </c>
       <c r="D165">
-        <v>556</v>
+        <v>888</v>
       </c>
       <c r="E165">
-        <v>754</v>
+        <v>586</v>
       </c>
       <c r="F165">
-        <v>1.88</v>
+        <v>7.07</v>
       </c>
       <c r="G165">
-        <v>1.34</v>
+        <v>1.27</v>
       </c>
       <c r="H165">
         <v>1.2</v>
       </c>
       <c r="I165">
-        <v>75.09</v>
+        <v>74.58</v>
       </c>
     </row>
     <row r="166" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A166">
-        <v>166</v>
+        <v>178</v>
       </c>
       <c r="B166">
         <v>9</v>
       </c>
       <c r="C166">
-        <v>6</v>
+        <v>18</v>
       </c>
       <c r="D166">
-        <v>587</v>
+        <v>912</v>
       </c>
       <c r="E166">
-        <v>754</v>
+        <v>586</v>
       </c>
       <c r="F166">
-        <v>2.29</v>
+        <v>7.51</v>
       </c>
       <c r="G166">
-        <v>1.34</v>
+        <v>1.27</v>
       </c>
       <c r="H166">
         <v>1.2</v>
       </c>
       <c r="I166">
-        <v>75.63</v>
+        <v>74.174000000000007</v>
       </c>
     </row>
     <row r="167" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A167">
-        <v>167</v>
+        <v>179</v>
       </c>
       <c r="B167">
         <v>9</v>
       </c>
       <c r="C167">
-        <v>7</v>
+        <v>19</v>
       </c>
       <c r="D167">
-        <v>618</v>
+        <v>935</v>
       </c>
       <c r="E167">
-        <v>754</v>
+        <v>586</v>
       </c>
       <c r="F167">
-        <v>2.7</v>
+        <v>7.93</v>
       </c>
       <c r="G167">
-        <v>1.34</v>
+        <v>1.27</v>
       </c>
       <c r="H167">
         <v>1.2</v>
       </c>
       <c r="I167">
-        <v>76.010000000000005</v>
+        <v>73.7</v>
       </c>
     </row>
     <row r="168" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A168">
-        <v>168</v>
+        <v>181</v>
       </c>
       <c r="B168">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="C168">
-        <v>8</v>
+        <v>1</v>
       </c>
       <c r="D168">
-        <v>649</v>
+        <v>513</v>
       </c>
       <c r="E168">
-        <v>754</v>
+        <v>633</v>
       </c>
       <c r="F168">
-        <v>3.11</v>
+        <v>0.19</v>
       </c>
       <c r="G168">
-        <v>1.35</v>
+        <v>0.41</v>
       </c>
       <c r="H168">
         <v>1.2</v>
       </c>
       <c r="I168">
-        <v>76.260000000000005</v>
+        <v>72.33</v>
       </c>
     </row>
     <row r="169" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A169">
-        <v>169</v>
+        <v>182</v>
       </c>
       <c r="B169">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="C169">
-        <v>9</v>
+        <v>2</v>
       </c>
       <c r="D169">
-        <v>680</v>
+        <v>537</v>
       </c>
       <c r="E169">
-        <v>754</v>
+        <v>633</v>
       </c>
       <c r="F169">
-        <v>3.52</v>
+        <v>0.63</v>
       </c>
       <c r="G169">
-        <v>1.35</v>
+        <v>0.41</v>
       </c>
       <c r="H169">
         <v>1.2</v>
       </c>
       <c r="I169">
-        <v>76.38</v>
+        <v>72.733999999999995</v>
       </c>
     </row>
     <row r="170" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A170">
-        <v>170</v>
+        <v>183</v>
       </c>
       <c r="B170">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="C170">
-        <v>10</v>
+        <v>3</v>
       </c>
       <c r="D170">
-        <v>711</v>
+        <v>560</v>
       </c>
       <c r="E170">
-        <v>754</v>
+        <v>633</v>
       </c>
       <c r="F170">
-        <v>3.92</v>
+        <v>1.05</v>
       </c>
       <c r="G170">
-        <v>1.35</v>
+        <v>0.41</v>
       </c>
       <c r="H170">
         <v>1.2</v>
       </c>
       <c r="I170">
-        <v>76.53</v>
+        <v>73.099999999999994</v>
       </c>
     </row>
     <row r="171" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A171">
-        <v>171</v>
+        <v>184</v>
       </c>
       <c r="B171">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="C171">
-        <v>11</v>
+        <v>4</v>
       </c>
       <c r="D171">
-        <v>741</v>
+        <v>584</v>
       </c>
       <c r="E171">
-        <v>754</v>
+        <v>633</v>
       </c>
       <c r="F171">
-        <v>4.33</v>
+        <v>1.49</v>
       </c>
       <c r="G171">
-        <v>1.35</v>
+        <v>0.41</v>
       </c>
       <c r="H171">
         <v>1.2</v>
       </c>
       <c r="I171">
-        <v>76.27</v>
+        <v>73.47</v>
       </c>
     </row>
     <row r="172" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A172">
-        <v>172</v>
+        <v>185</v>
       </c>
       <c r="B172">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="C172">
-        <v>12</v>
+        <v>5</v>
       </c>
       <c r="D172">
-        <v>772</v>
+        <v>607</v>
       </c>
       <c r="E172">
-        <v>754</v>
+        <v>633</v>
       </c>
       <c r="F172">
-        <v>4.8099999999999996</v>
+        <v>1.91</v>
       </c>
       <c r="G172">
-        <v>1.36</v>
+        <v>0.41</v>
       </c>
       <c r="H172">
         <v>1.2</v>
       </c>
       <c r="I172">
-        <v>76.11</v>
+        <v>73.900000000000006</v>
       </c>
     </row>
     <row r="173" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A173">
-        <v>173</v>
+        <v>186</v>
       </c>
       <c r="B173">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="C173">
-        <v>13</v>
+        <v>6</v>
       </c>
       <c r="D173">
-        <v>803</v>
+        <v>630</v>
       </c>
       <c r="E173">
-        <v>754</v>
+        <v>633</v>
       </c>
       <c r="F173">
-        <v>5.2</v>
+        <v>2.34</v>
       </c>
       <c r="G173">
-        <v>1.35</v>
+        <v>0.41</v>
       </c>
       <c r="H173">
         <v>1.2</v>
       </c>
       <c r="I173">
-        <v>75.819999999999993</v>
+        <v>74.3</v>
       </c>
     </row>
     <row r="174" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A174">
-        <v>174</v>
+        <v>187</v>
       </c>
       <c r="B174">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="C174">
-        <v>14</v>
+        <v>7</v>
       </c>
       <c r="D174">
-        <v>834</v>
+        <v>654</v>
       </c>
       <c r="E174">
-        <v>754</v>
+        <v>633</v>
       </c>
       <c r="F174">
-        <v>5.6</v>
+        <v>2.78</v>
       </c>
       <c r="G174">
-        <v>1.35</v>
+        <v>0.41</v>
       </c>
       <c r="H174">
         <v>1.2</v>
       </c>
       <c r="I174">
-        <v>75.459999999999994</v>
+        <v>74.849999999999994</v>
       </c>
     </row>
     <row r="175" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A175">
-        <v>175</v>
+        <v>188</v>
       </c>
       <c r="B175">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="C175">
-        <v>15</v>
+        <v>8</v>
       </c>
       <c r="D175">
-        <v>865</v>
+        <v>677</v>
       </c>
       <c r="E175">
-        <v>754</v>
+        <v>633</v>
       </c>
       <c r="F175">
-        <v>6</v>
+        <v>3.2</v>
       </c>
       <c r="G175">
-        <v>1.35</v>
+        <v>0.41</v>
       </c>
       <c r="H175">
         <v>1.2</v>
       </c>
       <c r="I175">
-        <v>75.13</v>
+        <v>75.08</v>
       </c>
     </row>
     <row r="176" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A176">
-        <v>176</v>
+        <v>189</v>
       </c>
       <c r="B176">
+        <v>10</v>
+      </c>
+      <c r="C176">
         <v>9</v>
       </c>
-      <c r="C176">
-        <v>16</v>
-      </c>
       <c r="D176">
-        <v>896</v>
+        <v>701</v>
       </c>
       <c r="E176">
-        <v>754</v>
+        <v>633</v>
       </c>
       <c r="F176">
-        <v>6.39</v>
+        <v>3.64</v>
       </c>
       <c r="G176">
-        <v>1.35</v>
+        <v>0.41</v>
       </c>
       <c r="H176">
         <v>1.2</v>
       </c>
       <c r="I176">
-        <v>7482</v>
+        <v>75.224000000000004</v>
       </c>
     </row>
     <row r="177" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A177">
-        <v>177</v>
+        <v>190</v>
       </c>
       <c r="B177">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="C177">
-        <v>17</v>
+        <v>10</v>
       </c>
       <c r="D177">
-        <v>927</v>
+        <v>724</v>
       </c>
       <c r="E177">
-        <v>754</v>
+        <v>633</v>
       </c>
       <c r="F177">
-        <v>6.89</v>
+        <v>4.0599999999999996</v>
       </c>
       <c r="G177">
-        <v>1.3</v>
+        <v>0.41</v>
       </c>
       <c r="H177">
         <v>1.2</v>
       </c>
       <c r="I177">
-        <v>74460</v>
+        <v>75.06</v>
       </c>
     </row>
     <row r="178" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A178">
-        <v>178</v>
+        <v>191</v>
       </c>
       <c r="B178">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="C178">
-        <v>18</v>
+        <v>11</v>
       </c>
       <c r="D178">
-        <v>958</v>
+        <v>748</v>
       </c>
       <c r="E178">
-        <v>754</v>
+        <v>633</v>
       </c>
       <c r="F178">
-        <v>7.3</v>
+        <v>4.5</v>
       </c>
       <c r="G178">
-        <v>1.31</v>
+        <v>0.41</v>
       </c>
       <c r="H178">
         <v>1.2</v>
       </c>
       <c r="I178">
-        <v>74.08</v>
+        <v>75.040000000000006</v>
       </c>
     </row>
     <row r="179" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A179">
-        <v>179</v>
+        <v>192</v>
       </c>
       <c r="B179">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="C179">
-        <v>19</v>
+        <v>12</v>
       </c>
       <c r="D179">
-        <v>989</v>
+        <v>771</v>
       </c>
       <c r="E179">
-        <v>754</v>
+        <v>633</v>
       </c>
       <c r="F179">
-        <v>7.7</v>
+        <v>4.92</v>
       </c>
       <c r="G179">
-        <v>1.32</v>
+        <v>0.41</v>
       </c>
       <c r="H179">
         <v>1.2</v>
       </c>
       <c r="I179">
-        <v>73.7</v>
+        <v>74.91</v>
       </c>
     </row>
     <row r="180" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A180">
-        <v>180</v>
+        <v>193</v>
       </c>
       <c r="B180">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="C180">
-        <v>20</v>
+        <v>13</v>
       </c>
       <c r="D180">
-        <v>1020</v>
+        <v>795</v>
       </c>
       <c r="E180">
-        <v>754</v>
+        <v>633</v>
       </c>
       <c r="F180">
-        <v>8.07</v>
+        <v>5.36</v>
       </c>
       <c r="G180">
-        <v>1.33</v>
+        <v>0.41</v>
       </c>
       <c r="H180">
         <v>1.2</v>
       </c>
       <c r="I180">
-        <v>73.23</v>
+        <v>74.69</v>
       </c>
     </row>
     <row r="181" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A181">
-        <v>181</v>
+        <v>195</v>
       </c>
       <c r="B181">
         <v>10</v>
       </c>
       <c r="C181">
-        <v>1</v>
+        <v>15</v>
       </c>
       <c r="D181">
-        <v>432</v>
+        <v>842</v>
       </c>
       <c r="E181">
-        <v>817</v>
+        <v>633</v>
       </c>
       <c r="F181">
-        <v>0.26</v>
+        <v>6.22</v>
       </c>
       <c r="G181">
-        <v>0.47</v>
+        <v>0.41</v>
       </c>
       <c r="H181">
         <v>1.2</v>
       </c>
       <c r="I181">
-        <v>71.87</v>
+        <v>74.19</v>
       </c>
     </row>
     <row r="182" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A182">
-        <v>182</v>
+        <v>196</v>
       </c>
       <c r="B182">
         <v>10</v>
       </c>
       <c r="C182">
-        <v>2</v>
+        <v>16</v>
       </c>
       <c r="D182">
-        <v>463</v>
+        <v>865</v>
       </c>
       <c r="E182">
-        <v>817</v>
+        <v>633</v>
       </c>
       <c r="F182">
-        <v>0.66</v>
+        <v>6.65</v>
       </c>
       <c r="G182">
-        <v>0.51</v>
+        <v>0.41</v>
       </c>
       <c r="H182">
         <v>1.2</v>
       </c>
       <c r="I182">
-        <v>72.110799999999998</v>
+        <v>73.900000000000006</v>
       </c>
     </row>
     <row r="183" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A183">
-        <v>183</v>
+        <v>197</v>
       </c>
       <c r="B183">
         <v>10</v>
       </c>
       <c r="C183">
-        <v>3</v>
+        <v>17</v>
       </c>
       <c r="D183">
-        <v>494</v>
+        <v>888</v>
       </c>
       <c r="E183">
-        <v>817</v>
+        <v>633</v>
       </c>
       <c r="F183">
-        <v>1.07</v>
+        <v>7.07</v>
       </c>
       <c r="G183">
-        <v>0.51</v>
+        <v>0.41</v>
       </c>
       <c r="H183">
         <v>1.2</v>
       </c>
       <c r="I183">
-        <v>72.510000000000005</v>
+        <v>73.44</v>
       </c>
     </row>
     <row r="184" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A184">
-        <v>184</v>
+        <v>198</v>
       </c>
       <c r="B184">
         <v>10</v>
       </c>
       <c r="C184">
-        <v>4</v>
+        <v>18</v>
       </c>
       <c r="D184">
-        <v>525</v>
+        <v>912</v>
       </c>
       <c r="E184">
-        <v>817</v>
+        <v>633</v>
       </c>
       <c r="F184">
-        <v>1.47</v>
+        <v>7.51</v>
       </c>
       <c r="G184">
-        <v>0.51</v>
+        <v>0.41</v>
       </c>
       <c r="H184">
         <v>1.2</v>
       </c>
       <c r="I184">
-        <v>72.87</v>
+        <v>73.123999999999995</v>
       </c>
     </row>
     <row r="185" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A185">
-        <v>185</v>
+        <v>199</v>
       </c>
       <c r="B185">
         <v>10</v>
       </c>
       <c r="C185">
-        <v>5</v>
+        <v>19</v>
       </c>
       <c r="D185">
-        <v>556</v>
+        <v>935</v>
       </c>
       <c r="E185">
-        <v>817</v>
+        <v>633</v>
       </c>
       <c r="F185">
-        <v>1.88</v>
+        <v>7.93</v>
       </c>
       <c r="G185">
-        <v>0.51</v>
+        <v>0.41</v>
       </c>
       <c r="H185">
         <v>1.2</v>
       </c>
       <c r="I185">
-        <v>73.260000000000005</v>
-      </c>
-    </row>
-    <row r="186" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A186">
-        <v>186</v>
-      </c>
-      <c r="B186">
-        <v>10</v>
-      </c>
-      <c r="C186">
-        <v>6</v>
-      </c>
-      <c r="D186">
-        <v>587</v>
-      </c>
-      <c r="E186">
-        <v>817</v>
-      </c>
-      <c r="F186">
-        <v>2.29</v>
-      </c>
-      <c r="G186">
-        <v>0.51</v>
-      </c>
-      <c r="H186">
-        <v>1.2</v>
-      </c>
-      <c r="I186">
-        <v>73.69</v>
-      </c>
-    </row>
-    <row r="187" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A187">
-        <v>187</v>
-      </c>
-      <c r="B187">
-        <v>10</v>
-      </c>
-      <c r="C187">
-        <v>7</v>
-      </c>
-      <c r="D187">
-        <v>618</v>
-      </c>
-      <c r="E187">
-        <v>817</v>
-      </c>
-      <c r="F187">
-        <v>2.71</v>
-      </c>
-      <c r="G187">
-        <v>52</v>
-      </c>
-      <c r="H187">
-        <v>1.2</v>
-      </c>
-      <c r="I187">
-        <v>740108</v>
-      </c>
-    </row>
-    <row r="188" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A188">
-        <v>188</v>
-      </c>
-      <c r="B188">
-        <v>10</v>
-      </c>
-      <c r="C188">
-        <v>8</v>
-      </c>
-      <c r="D188">
-        <v>649</v>
-      </c>
-      <c r="E188">
-        <v>817</v>
-      </c>
-      <c r="F188">
-        <v>3.12</v>
-      </c>
-      <c r="G188">
-        <v>0.52</v>
-      </c>
-      <c r="H188">
-        <v>1.2</v>
-      </c>
-      <c r="I188">
-        <v>74.25</v>
-      </c>
-    </row>
-    <row r="189" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A189">
-        <v>189</v>
-      </c>
-      <c r="B189">
-        <v>10</v>
-      </c>
-      <c r="C189">
-        <v>9</v>
-      </c>
-      <c r="D189">
-        <v>680</v>
-      </c>
-      <c r="E189">
-        <v>817</v>
-      </c>
-      <c r="F189">
-        <v>3.53</v>
-      </c>
-      <c r="G189">
-        <v>0.52</v>
-      </c>
-      <c r="H189">
-        <v>1.2</v>
-      </c>
-      <c r="I189">
-        <v>744108</v>
-      </c>
-    </row>
-    <row r="190" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A190">
-        <v>190</v>
-      </c>
-      <c r="B190">
-        <v>10</v>
-      </c>
-      <c r="C190">
-        <v>10</v>
-      </c>
-      <c r="D190">
-        <v>711</v>
-      </c>
-      <c r="E190">
-        <v>817</v>
-      </c>
-      <c r="F190">
-        <v>3.94</v>
-      </c>
-      <c r="G190">
-        <v>0.52</v>
-      </c>
-      <c r="H190">
-        <v>1.2</v>
-      </c>
-      <c r="I190">
-        <v>7449</v>
-      </c>
-    </row>
-    <row r="191" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A191">
-        <v>191</v>
-      </c>
-      <c r="B191">
-        <v>10</v>
-      </c>
-      <c r="C191">
-        <v>11</v>
-      </c>
-      <c r="D191">
-        <v>741</v>
-      </c>
-      <c r="E191">
-        <v>817</v>
-      </c>
-      <c r="F191">
-        <v>4.3499999999999996</v>
-      </c>
-      <c r="G191">
-        <v>0.52</v>
-      </c>
-      <c r="H191">
-        <v>1.2</v>
-      </c>
-      <c r="I191">
-        <v>7448</v>
-      </c>
-    </row>
-    <row r="192" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A192">
-        <v>192</v>
-      </c>
-      <c r="B192">
-        <v>10</v>
-      </c>
-      <c r="C192">
-        <v>12</v>
-      </c>
-      <c r="D192">
-        <v>772</v>
-      </c>
-      <c r="E192">
-        <v>817</v>
-      </c>
-      <c r="F192">
-        <v>4.75</v>
-      </c>
-      <c r="G192">
-        <v>0.53</v>
-      </c>
-      <c r="H192">
-        <v>1.2</v>
-      </c>
-      <c r="I192">
-        <v>744108</v>
-      </c>
-    </row>
-    <row r="193" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A193">
-        <v>193</v>
-      </c>
-      <c r="B193">
-        <v>10</v>
-      </c>
-      <c r="C193">
-        <v>13</v>
-      </c>
-      <c r="D193">
-        <v>803</v>
-      </c>
-      <c r="E193">
-        <v>817</v>
-      </c>
-      <c r="F193">
-        <v>5.15</v>
-      </c>
-      <c r="G193">
-        <v>0.53</v>
-      </c>
-      <c r="H193">
-        <v>1.2</v>
-      </c>
-      <c r="I193">
-        <v>74.28</v>
-      </c>
-    </row>
-    <row r="194" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A194">
-        <v>194</v>
-      </c>
-      <c r="B194">
-        <v>10</v>
-      </c>
-      <c r="C194">
-        <v>14</v>
-      </c>
-      <c r="D194">
-        <v>834</v>
-      </c>
-      <c r="E194">
-        <v>817</v>
-      </c>
-      <c r="F194">
-        <v>5.66</v>
-      </c>
-      <c r="G194">
-        <v>0.47</v>
-      </c>
-      <c r="H194">
-        <v>1.2</v>
-      </c>
-      <c r="I194">
-        <v>74.09</v>
-      </c>
-    </row>
-    <row r="195" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A195">
-        <v>195</v>
-      </c>
-      <c r="B195">
-        <v>10</v>
-      </c>
-      <c r="C195">
-        <v>15</v>
-      </c>
-      <c r="D195">
-        <v>865</v>
-      </c>
-      <c r="E195">
-        <v>817</v>
-      </c>
-      <c r="F195">
-        <v>5.98</v>
-      </c>
-      <c r="G195">
-        <v>0.53</v>
-      </c>
-      <c r="H195">
-        <v>1.2</v>
-      </c>
-      <c r="I195">
-        <v>73.86</v>
-      </c>
-    </row>
-    <row r="196" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A196">
-        <v>196</v>
-      </c>
-      <c r="B196">
-        <v>10</v>
-      </c>
-      <c r="C196">
-        <v>16</v>
-      </c>
-      <c r="D196">
-        <v>896</v>
-      </c>
-      <c r="E196">
-        <v>817</v>
-      </c>
-      <c r="F196">
-        <v>6.49</v>
-      </c>
-      <c r="G196">
-        <v>0.48</v>
-      </c>
-      <c r="H196">
-        <v>1.2</v>
-      </c>
-      <c r="I196">
-        <v>73.61</v>
-      </c>
-    </row>
-    <row r="197" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A197">
-        <v>197</v>
-      </c>
-      <c r="B197">
-        <v>10</v>
-      </c>
-      <c r="C197">
-        <v>17</v>
-      </c>
-      <c r="D197">
-        <v>927</v>
-      </c>
-      <c r="E197">
-        <v>817</v>
-      </c>
-      <c r="F197">
-        <v>6.89</v>
-      </c>
-      <c r="G197">
-        <v>0.48</v>
-      </c>
-      <c r="H197">
-        <v>1.2</v>
-      </c>
-      <c r="I197">
-        <v>73.34</v>
-      </c>
-    </row>
-    <row r="198" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A198">
-        <v>198</v>
-      </c>
-      <c r="B198">
-        <v>10</v>
-      </c>
-      <c r="C198">
-        <v>18</v>
-      </c>
-      <c r="D198">
-        <v>958</v>
-      </c>
-      <c r="E198">
-        <v>817</v>
-      </c>
-      <c r="F198">
-        <v>7.3</v>
-      </c>
-      <c r="G198">
-        <v>0.48</v>
-      </c>
-      <c r="H198">
-        <v>1.2</v>
-      </c>
-      <c r="I198">
-        <v>73.05</v>
-      </c>
-    </row>
-    <row r="199" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A199">
-        <v>199</v>
-      </c>
-      <c r="B199">
-        <v>10</v>
-      </c>
-      <c r="C199">
-        <v>19</v>
-      </c>
-      <c r="D199">
-        <v>989</v>
-      </c>
-      <c r="E199">
-        <v>817</v>
-      </c>
-      <c r="F199">
-        <v>7.71</v>
-      </c>
-      <c r="G199">
-        <v>0.49</v>
-      </c>
-      <c r="H199">
-        <v>1.2</v>
-      </c>
-      <c r="I199">
-        <v>72.760000000000005</v>
-      </c>
-    </row>
-    <row r="200" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A200">
-        <v>200</v>
-      </c>
-      <c r="B200">
-        <v>10</v>
-      </c>
-      <c r="C200">
-        <v>20</v>
-      </c>
-      <c r="D200">
-        <v>1020</v>
-      </c>
-      <c r="E200">
-        <v>817</v>
-      </c>
-      <c r="F200">
-        <v>8.1199999999999992</v>
-      </c>
-      <c r="G200">
-        <v>0.49</v>
-      </c>
-      <c r="H200">
-        <v>1.2</v>
-      </c>
-      <c r="I200">
-        <v>72.459999999999994</v>
+        <v>72.8</v>
       </c>
     </row>
   </sheetData>
+  <autoFilter ref="A1:I1"/>
   <phoneticPr fontId="1" type="noConversion"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
   <pageSetup paperSize="9" orientation="portrait" horizontalDpi="4294967294" verticalDpi="300" r:id="rId1"/>
